--- a/database/event/3647/event_3647_evp_summary.xlsx
+++ b/database/event/3647/event_3647_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2995</v>
+        <v>6.3091</v>
       </c>
       <c r="C2" t="n">
-        <v>1.074</v>
+        <v>1.2786</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7195</v>
+        <v>2.0696</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2995</v>
+        <v>6.3091</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7345</v>
+        <v>3.7441</v>
       </c>
       <c r="G2" t="n">
         <v>2.565</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7345</v>
+        <v>3.7441</v>
       </c>
       <c r="I2" t="n">
-        <v>2.76</v>
+        <v>3.8074</v>
       </c>
       <c r="J2" t="n">
         <v>2.565</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>5.324999999999999</v>
+        <v>6.3724</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.0838</v>
+        <v>5.2419</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8276</v>
+        <v>1.0623</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2284</v>
+        <v>1.6445</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0838</v>
+        <v>5.2419</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4144</v>
+        <v>4.5725</v>
       </c>
       <c r="G3" t="n">
         <v>0.6694</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4144</v>
+        <v>4.8667</v>
       </c>
       <c r="I3" t="n">
-        <v>3.4462</v>
+        <v>4.9489</v>
       </c>
       <c r="J3" t="n">
         <v>0.6694</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>4.115600000000001</v>
+        <v>5.6183</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.9793</v>
+        <v>4.9556</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8065</v>
+        <v>1.0043</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1862</v>
+        <v>1.5304</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9793</v>
+        <v>4.9556</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4985</v>
+        <v>4.4748</v>
       </c>
       <c r="G4" t="n">
         <v>0.4808</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4985</v>
+        <v>4.7134</v>
       </c>
       <c r="I4" t="n">
-        <v>3.5312</v>
+        <v>4.793</v>
       </c>
       <c r="J4" t="n">
         <v>0.4808</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.012</v>
+        <v>5.2738</v>
       </c>
       <c r="N4" t="n">
         <v>193</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7344</v>
+        <v>4.159</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7568</v>
+        <v>0.8429</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0873</v>
+        <v>1.213</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7344</v>
+        <v>4.159</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4162</v>
+        <v>2.8408</v>
       </c>
       <c r="G5" t="n">
         <v>1.3182</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4162</v>
+        <v>2.8408</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4387</v>
+        <v>2.8888</v>
       </c>
       <c r="J5" t="n">
         <v>1.3182</v>
@@ -667,7 +667,7 @@
         <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7569</v>
+        <v>4.207</v>
       </c>
       <c r="N5" t="n">
         <v>193</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.339</v>
+        <v>3.6667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.474</v>
+        <v>0.7431</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5235</v>
+        <v>1.0169</v>
       </c>
       <c r="E6" t="n">
-        <v>2.339</v>
+        <v>3.6667</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3797</v>
+        <v>3.7074</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0407</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3797</v>
+        <v>3.7074</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3797</v>
+        <v>3.7074</v>
       </c>
       <c r="J6" t="n">
         <v>-0.0407</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>2.339</v>
+        <v>3.6667</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.0877</v>
+        <v>3.3175</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4231</v>
+        <v>0.6723</v>
       </c>
       <c r="D7" t="n">
-        <v>0.422</v>
+        <v>0.8778</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0877</v>
+        <v>3.3175</v>
       </c>
       <c r="F7" t="n">
-        <v>2.3903</v>
+        <v>3.6201</v>
       </c>
       <c r="G7" t="n">
         <v>-0.3026</v>
       </c>
       <c r="H7" t="n">
-        <v>2.3903</v>
+        <v>3.6201</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4126</v>
+        <v>3.6813</v>
       </c>
       <c r="J7" t="n">
         <v>-0.3026</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>2.11</v>
+        <v>3.3787</v>
       </c>
       <c r="N7" t="n">
         <v>193</v>
@@ -768,47 +768,47 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3362</v>
+        <v>0.5056</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2489</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1.6591</v>
+        <v>2.4946</v>
       </c>
       <c r="N8" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="C9" t="n">
-        <v>0.3137</v>
+        <v>0.4282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.204</v>
+        <v>0.3978</v>
       </c>
       <c r="E9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.5479</v>
+        <v>2.1128</v>
       </c>
       <c r="N9" t="n">
         <v>139</v>
@@ -860,461 +860,461 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7433999999999999</v>
+        <v>1.8022</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1507</v>
+        <v>0.3652</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.121</v>
+        <v>0.2741</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7433999999999999</v>
+        <v>1.8022</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4799</v>
+        <v>1.8022</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7365</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.4799</v>
+        <v>1.8022</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4799</v>
+        <v>1.8022</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7365</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L10" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.7433999999999999</v>
+        <v>1.8022</v>
       </c>
       <c r="N10" t="n">
-        <v>208</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7286</v>
+        <v>1.3061</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1477</v>
+        <v>0.2647</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.127</v>
+        <v>0.0764</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7286</v>
+        <v>1.3061</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7286</v>
+        <v>1.2552</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.0509</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7286</v>
+        <v>1.2552</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7286</v>
+        <v>1.2552</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>0.0509</v>
       </c>
       <c r="K11" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7286</v>
+        <v>1.3061</v>
       </c>
       <c r="N11" t="n">
-        <v>128</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5469000000000001</v>
+        <v>1.2067</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1108</v>
+        <v>0.2446</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2004</v>
+        <v>0.0368</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5469000000000001</v>
+        <v>1.2067</v>
       </c>
       <c r="F12" t="n">
-        <v>0.496</v>
+        <v>1.2067</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0509</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.496</v>
+        <v>1.2067</v>
       </c>
       <c r="I12" t="n">
-        <v>0.496</v>
+        <v>1.2067</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0509</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5468999999999999</v>
+        <v>1.2067</v>
       </c>
       <c r="N12" t="n">
-        <v>208</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4638</v>
+        <v>1.0018</v>
       </c>
       <c r="C13" t="n">
-        <v>0.094</v>
+        <v>0.203</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.234</v>
+        <v>-0.0448</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4638</v>
+        <v>1.0018</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4638</v>
+        <v>1.7383</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.7365</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4638</v>
+        <v>1.7383</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4638</v>
+        <v>1.7383</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.7365</v>
       </c>
       <c r="K13" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4638</v>
+        <v>1.0018</v>
       </c>
       <c r="N13" t="n">
-        <v>130</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0589</v>
+        <v>0.1014</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3039</v>
+        <v>-0.2445</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2907</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="C15" t="n">
-        <v>0.031</v>
+        <v>0.094</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3596</v>
+        <v>-0.2591</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1528</v>
+        <v>0.4638</v>
       </c>
       <c r="N15" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0075</v>
+        <v>0.0769</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4362</v>
+        <v>-0.2927</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0368</v>
+        <v>0.3795</v>
       </c>
       <c r="N16" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Golden</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0076</v>
+        <v>0.0331</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4365</v>
+        <v>-0.3789</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0374</v>
+        <v>0.1631</v>
       </c>
       <c r="N17" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Golden</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1142</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0231</v>
+        <v>0.014</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4675</v>
+        <v>-0.4164</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1142</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2253</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3395</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2253</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2253</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3395</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L18" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1142</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>208</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.285</v>
+        <v>-0.0922</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0578</v>
+        <v>-0.0187</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5365</v>
+        <v>-0.4806</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.285</v>
+        <v>-0.0922</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.285</v>
+        <v>0.2473</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0.3395</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.285</v>
+        <v>0.2473</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.285</v>
+        <v>0.2473</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.3395</v>
       </c>
       <c r="K19" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.285</v>
+        <v>-0.09220000000000003</v>
       </c>
       <c r="N19" t="n">
-        <v>139</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0653</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5571</v>
+        <v>-0.5723</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3361</v>
+        <v>-0.3222</v>
       </c>
       <c r="N20" t="n">
         <v>128</v>
@@ -1376,7 +1376,7 @@
         <v>-0.0896</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6</v>
+        <v>-0.6201</v>
       </c>
       <c r="E21" t="n">
         <v>-0.4422</v>
@@ -1422,7 +1422,7 @@
         <v>-0.1218</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6642</v>
+        <v>-0.6834</v>
       </c>
       <c r="E22" t="n">
         <v>-0.6012</v>
@@ -1458,32 +1458,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1746</v>
+        <v>-0.1595</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7694</v>
+        <v>-0.7575</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8616</v>
+        <v>-0.7872</v>
       </c>
       <c r="N23" t="n">
         <v>128</v>
@@ -1504,124 +1504,124 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1768</v>
+        <v>-0.1746</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7738</v>
+        <v>-0.7872</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8724</v>
+        <v>-0.8616</v>
       </c>
       <c r="N24" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1874</v>
+        <v>-0.1749</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7949000000000001</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9247</v>
+        <v>-0.8631</v>
       </c>
       <c r="N25" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1962</v>
+        <v>-0.1874</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8125</v>
+        <v>-0.8123</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9681</v>
+        <v>-0.9247</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1652,7 +1652,7 @@
         <v>-0.2527</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9251</v>
+        <v>-0.9407</v>
       </c>
       <c r="E27" t="n">
         <v>-1.247</v>
@@ -1698,7 +1698,7 @@
         <v>-0.2702</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9599</v>
+        <v>-0.975</v>
       </c>
       <c r="E28" t="n">
         <v>-1.3331</v>
@@ -1744,7 +1744,7 @@
         <v>-0.2935</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0064</v>
+        <v>-1.0209</v>
       </c>
       <c r="E29" t="n">
         <v>-1.4482</v>
@@ -1790,7 +1790,7 @@
         <v>-0.3004</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0201</v>
+        <v>-1.0344</v>
       </c>
       <c r="E30" t="n">
         <v>-1.4822</v>
@@ -1836,7 +1836,7 @@
         <v>-0.4792</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.3766</v>
+        <v>-1.386</v>
       </c>
       <c r="E31" t="n">
         <v>-2.3647</v>

--- a/database/event/3647/event_3647_evp_summary.xlsx
+++ b/database/event/3647/event_3647_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.3091</v>
+        <v>5.2504</v>
       </c>
       <c r="C2" t="n">
-        <v>1.2786</v>
+        <v>1.0641</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0696</v>
+        <v>1.7323</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3091</v>
+        <v>5.2504</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7441</v>
+        <v>3.1303</v>
       </c>
       <c r="G2" t="n">
-        <v>2.565</v>
+        <v>2.1201</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7441</v>
+        <v>3.5139</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8074</v>
+        <v>3.8089</v>
       </c>
       <c r="J2" t="n">
-        <v>2.565</v>
+        <v>2.1201</v>
       </c>
       <c r="K2" t="n">
         <v>114</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>6.3724</v>
+        <v>5.929</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.2419</v>
+        <v>4.4189</v>
       </c>
       <c r="C3" t="n">
-        <v>1.0623</v>
+        <v>0.8955</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6445</v>
+        <v>1.3569</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2419</v>
+        <v>4.4189</v>
       </c>
       <c r="F3" t="n">
-        <v>4.5725</v>
+        <v>3.5585</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6694</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>4.8667</v>
+        <v>4.4541</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9489</v>
+        <v>4.828</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6694</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6183</v>
+        <v>5.688400000000001</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -584,35 +584,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Xyp9x</t>
+          <t>gla1ve</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.9556</v>
+        <v>4.345</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0043</v>
+        <v>0.8806</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5304</v>
+        <v>1.3235</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9556</v>
+        <v>4.345</v>
       </c>
       <c r="F4" t="n">
-        <v>4.4748</v>
+        <v>2.8723</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4808</v>
+        <v>1.4727</v>
       </c>
       <c r="H4" t="n">
-        <v>4.7134</v>
+        <v>2.9474</v>
       </c>
       <c r="I4" t="n">
-        <v>4.793</v>
+        <v>3.1948</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4808</v>
+        <v>1.4727</v>
       </c>
       <c r="K4" t="n">
         <v>114</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2738</v>
+        <v>4.6675</v>
       </c>
       <c r="N4" t="n">
         <v>193</v>
@@ -630,35 +630,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gla1ve</t>
+          <t>Xyp9x</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.159</v>
+        <v>4.2069</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8429</v>
+        <v>0.8526</v>
       </c>
       <c r="D5" t="n">
-        <v>1.213</v>
+        <v>1.2612</v>
       </c>
       <c r="E5" t="n">
-        <v>4.159</v>
+        <v>4.2069</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8408</v>
+        <v>3.5766</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3182</v>
+        <v>0.6303</v>
       </c>
       <c r="H5" t="n">
-        <v>2.8408</v>
+        <v>4.4938</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8888</v>
+        <v>4.8711</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3182</v>
+        <v>0.6303</v>
       </c>
       <c r="K5" t="n">
         <v>114</v>
@@ -667,7 +667,7 @@
         <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>4.207</v>
+        <v>5.5014</v>
       </c>
       <c r="N5" t="n">
         <v>193</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6667</v>
+        <v>3.363</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7431</v>
+        <v>0.6816</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0169</v>
+        <v>0.8802</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6667</v>
+        <v>3.363</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7074</v>
+        <v>3.0564</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0407</v>
+        <v>0.3066</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7074</v>
+        <v>3.3515</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7074</v>
+        <v>3.3515</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.0407</v>
+        <v>0.3066</v>
       </c>
       <c r="K6" t="n">
         <v>129</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6667</v>
+        <v>3.6581</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3175</v>
+        <v>2.7481</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6723</v>
+        <v>0.5569</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8778</v>
+        <v>0.6026</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3175</v>
+        <v>2.7481</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6201</v>
+        <v>3.0674</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3026</v>
+        <v>-0.3193</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6201</v>
+        <v>3.3757</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6813</v>
+        <v>3.6591</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3026</v>
+        <v>-0.3193</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3787</v>
+        <v>3.3398</v>
       </c>
       <c r="N7" t="n">
         <v>193</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5056</v>
+        <v>0.5242</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5298</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4946</v>
+        <v>2.5868</v>
       </c>
       <c r="N8" t="n">
         <v>128</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4282</v>
+        <v>0.4529</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3978</v>
+        <v>0.3708</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1128</v>
+        <v>2.2347</v>
       </c>
       <c r="N9" t="n">
         <v>139</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3652</v>
+        <v>0.4094</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2741</v>
+        <v>0.274</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8022</v>
+        <v>2.0201</v>
       </c>
       <c r="N10" t="n">
         <v>139</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3061</v>
+        <v>1.5757</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2647</v>
+        <v>0.3193</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0764</v>
+        <v>0.0733</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3061</v>
+        <v>1.5757</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2552</v>
+        <v>1.5002</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0509</v>
+        <v>0.0755</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2552</v>
+        <v>1.5002</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2552</v>
+        <v>1.5002</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0509</v>
+        <v>0.0755</v>
       </c>
       <c r="K11" t="n">
         <v>129</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.3061</v>
+        <v>1.5757</v>
       </c>
       <c r="N11" t="n">
         <v>208</v>
@@ -952,185 +952,185 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2067</v>
+        <v>1.5525</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2446</v>
+        <v>0.3146</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0368</v>
+        <v>0.0629</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2067</v>
+        <v>1.5525</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2067</v>
+        <v>2.0129</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.4604</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2067</v>
+        <v>2.0129</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2067</v>
+        <v>2.0129</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0.4604</v>
       </c>
       <c r="K12" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2067</v>
+        <v>1.5525</v>
       </c>
       <c r="N12" t="n">
-        <v>139</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.0018</v>
+        <v>1.2038</v>
       </c>
       <c r="C13" t="n">
-        <v>0.203</v>
+        <v>0.244</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0448</v>
+        <v>-0.0946</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0018</v>
+        <v>1.2038</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7383</v>
+        <v>1.2038</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.7365</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7383</v>
+        <v>1.2038</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7383</v>
+        <v>1.2038</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7365</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L13" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0018</v>
+        <v>1.2038</v>
       </c>
       <c r="N13" t="n">
-        <v>208</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1014</v>
+        <v>0.167</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2445</v>
+        <v>-0.2661</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.8239</v>
       </c>
       <c r="N14" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="C15" t="n">
-        <v>0.094</v>
+        <v>0.156</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2591</v>
+        <v>-0.2906</v>
       </c>
       <c r="E15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4638</v>
+        <v>0.7696</v>
       </c>
       <c r="N15" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0769</v>
+        <v>0.1487</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2927</v>
+        <v>-0.3068</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3795</v>
+        <v>0.7336</v>
       </c>
       <c r="N16" t="n">
         <v>139</v>
@@ -1182,32 +1182,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0331</v>
+        <v>0.1465</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3789</v>
+        <v>-0.3116</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1631</v>
+        <v>0.7231</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="C18" t="n">
-        <v>0.014</v>
+        <v>0.0859</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4164</v>
+        <v>-0.4467</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="I18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.4237</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-0.0922</v>
+        <v>0.3076</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0187</v>
+        <v>0.0623</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4806</v>
+        <v>-0.4991</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0922</v>
+        <v>0.3076</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2473</v>
+        <v>0.4985</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3395</v>
+        <v>-0.1909</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2473</v>
+        <v>0.4985</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2473</v>
+        <v>0.4985</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3395</v>
+        <v>-0.1909</v>
       </c>
       <c r="K19" t="n">
         <v>129</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.09220000000000003</v>
+        <v>0.3076</v>
       </c>
       <c r="N19" t="n">
         <v>208</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0653</v>
+        <v>-0.0118</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5723</v>
+        <v>-0.6642</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.3222</v>
+        <v>-0.0581</v>
       </c>
       <c r="N20" t="n">
         <v>128</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0896</v>
+        <v>-0.0152</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6201</v>
+        <v>-0.672</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4422</v>
+        <v>-0.0752</v>
       </c>
       <c r="N21" t="n">
         <v>139</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.1218</v>
+        <v>-0.0355</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6834</v>
+        <v>-0.717</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6012</v>
+        <v>-0.175</v>
       </c>
       <c r="N22" t="n">
         <v>130</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.1595</v>
+        <v>-0.062</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7575</v>
+        <v>-0.7762</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7872</v>
+        <v>-0.306</v>
       </c>
       <c r="N23" t="n">
         <v>128</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Calyx</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.1746</v>
+        <v>-0.0725</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7872</v>
+        <v>-0.7996</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.8616</v>
+        <v>-0.3579</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>Calyx</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1749</v>
+        <v>-0.0979</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.8562</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8631</v>
+        <v>-0.4833</v>
       </c>
       <c r="N25" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1874</v>
+        <v>-0.1106</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8123</v>
+        <v>-0.8844</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.9247</v>
+        <v>-0.5457</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-1.247</v>
+        <v>-0.6384</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.2527</v>
+        <v>-0.1294</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9407</v>
+        <v>-0.9262</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.247</v>
+        <v>-0.6384</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.247</v>
+        <v>0.2092</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.8476</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.247</v>
+        <v>0.2092</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.247</v>
+        <v>0.2092</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.8476</v>
       </c>
       <c r="K27" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.247</v>
+        <v>-0.6384000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>130</v>
+        <v>208</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-1.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.2702</v>
+        <v>-0.1306</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.975</v>
+        <v>-0.9288</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="G28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="J28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L28" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-1.3331</v>
+        <v>-0.6442</v>
       </c>
       <c r="N28" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ngiN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.2935</v>
+        <v>-0.1904</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0209</v>
+        <v>-1.0622</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-1.4482</v>
+        <v>-0.9395</v>
       </c>
       <c r="N29" t="n">
         <v>128</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>ngiN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.3004</v>
+        <v>-0.1981</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0344</v>
+        <v>-1.0794</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.4822</v>
+        <v>-0.9777</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.4792</v>
+        <v>-0.3818</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.386</v>
+        <v>-1.4885</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-2.3647</v>
+        <v>-1.8838</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3259</v>
+        <v>1.8681</v>
       </c>
       <c r="J2" t="n">
-        <v>44.1921</v>
+        <v>35.4939</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2515</v>
+        <v>1.2123</v>
       </c>
       <c r="J3" t="n">
-        <v>23.7785</v>
+        <v>23.0337</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2291</v>
+        <v>1.2011</v>
       </c>
       <c r="J4" t="n">
-        <v>23.3529</v>
+        <v>22.8209</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4555</v>
+        <v>0.5795</v>
       </c>
       <c r="J5" t="n">
-        <v>8.654500000000001</v>
+        <v>11.0105</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8851</v>
+        <v>-0.8474</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.8169</v>
+        <v>-16.1006</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2539</v>
+        <v>-0.2231</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.8241</v>
+        <v>-4.2389</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2844</v>
+        <v>-0.2458</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.4036</v>
+        <v>-4.6702</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.738</v>
+        <v>-0.5121</v>
       </c>
       <c r="J9" t="n">
-        <v>-14.022</v>
+        <v>-9.729900000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.39</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7967</v>
+        <v>-0.5508</v>
       </c>
       <c r="J10" t="n">
-        <v>-15.1373</v>
+        <v>-10.4652</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.64</v>
       </c>
       <c r="J11" t="n">
-        <v>-17.4781</v>
+        <v>-12.16</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5512</v>
+        <v>0.5018</v>
       </c>
       <c r="J12" t="n">
-        <v>16.536</v>
+        <v>15.054</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0128</v>
+        <v>-0.0118</v>
       </c>
       <c r="J13" t="n">
-        <v>0.384</v>
+        <v>-0.354</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0129</v>
+        <v>-0.0277</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.387</v>
+        <v>-0.831</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5155999999999999</v>
+        <v>-0.3352</v>
       </c>
       <c r="J15" t="n">
-        <v>-15.468</v>
+        <v>-10.056</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6317</v>
+        <v>-0.4194</v>
       </c>
       <c r="J16" t="n">
-        <v>-18.951</v>
+        <v>-12.582</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4286</v>
+        <v>0.3648</v>
       </c>
       <c r="J17" t="n">
-        <v>12.858</v>
+        <v>10.944</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2807</v>
+        <v>0.2401</v>
       </c>
       <c r="J18" t="n">
-        <v>8.420999999999999</v>
+        <v>7.203</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1862</v>
+        <v>0.1749</v>
       </c>
       <c r="J19" t="n">
-        <v>5.586</v>
+        <v>5.247</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1862</v>
+        <v>0.1749</v>
       </c>
       <c r="J20" t="n">
-        <v>5.586</v>
+        <v>5.247</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1894</v>
+        <v>-0.1003</v>
       </c>
       <c r="J21" t="n">
-        <v>-5.682</v>
+        <v>-3.009</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7208</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>21.624</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5697</v>
+        <v>0.5399</v>
       </c>
       <c r="J23" t="n">
-        <v>17.091</v>
+        <v>16.197</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0382</v>
+        <v>0.0785</v>
       </c>
       <c r="J24" t="n">
-        <v>1.146</v>
+        <v>2.355</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0665</v>
+        <v>-0.0167</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.995</v>
+        <v>-0.501</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3121</v>
+        <v>-0.2498</v>
       </c>
       <c r="J26" t="n">
-        <v>-9.363</v>
+        <v>-7.494</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5698</v>
+        <v>0.6825</v>
       </c>
       <c r="J27" t="n">
-        <v>17.094</v>
+        <v>20.475</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1491</v>
+        <v>0.1464</v>
       </c>
       <c r="J28" t="n">
-        <v>4.473</v>
+        <v>4.392</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0973</v>
+        <v>-0.0605</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.919</v>
+        <v>-1.815</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3758</v>
+        <v>-0.2352</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.274</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5142</v>
+        <v>-0.3326</v>
       </c>
       <c r="J31" t="n">
-        <v>-15.426</v>
+        <v>-9.978</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4552</v>
+        <v>0.5238</v>
       </c>
       <c r="J32" t="n">
-        <v>10.9248</v>
+        <v>12.5712</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3673</v>
+        <v>0.4049</v>
       </c>
       <c r="J33" t="n">
-        <v>8.815200000000001</v>
+        <v>9.717599999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2161</v>
+        <v>-0.1611</v>
       </c>
       <c r="J34" t="n">
-        <v>-5.1864</v>
+        <v>-3.8664</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.3922</v>
       </c>
       <c r="J35" t="n">
-        <v>-14.2128</v>
+        <v>-9.412800000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8827</v>
+        <v>-0.6116</v>
       </c>
       <c r="J36" t="n">
-        <v>-21.1848</v>
+        <v>-14.6784</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.9816</v>
+        <v>1.6826</v>
       </c>
       <c r="J37" t="n">
-        <v>47.5584</v>
+        <v>40.3824</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3729</v>
+        <v>1.2519</v>
       </c>
       <c r="J38" t="n">
-        <v>32.9496</v>
+        <v>30.0456</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.89</v>
+        <v>0.9502</v>
       </c>
       <c r="J39" t="n">
-        <v>21.36</v>
+        <v>22.8048</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0849</v>
+        <v>0.1734</v>
       </c>
       <c r="J40" t="n">
-        <v>2.0376</v>
+        <v>4.1616</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7199</v>
+        <v>-0.6615</v>
       </c>
       <c r="J41" t="n">
-        <v>-17.2776</v>
+        <v>-15.876</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>1.7282</v>
+        <v>1.4777</v>
       </c>
       <c r="J42" t="n">
-        <v>44.9332</v>
+        <v>38.4202</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.48</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1621</v>
+        <v>1.1068</v>
       </c>
       <c r="J43" t="n">
-        <v>30.2146</v>
+        <v>28.7768</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.1425</v>
       </c>
       <c r="J44" t="n">
-        <v>1.7576</v>
+        <v>3.705</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1373</v>
+        <v>-0.0585</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.5698</v>
+        <v>-1.521</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.442</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.3796</v>
+        <v>-11.492</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.43</v>
+        <v>0.4913</v>
       </c>
       <c r="J47" t="n">
-        <v>11.18</v>
+        <v>12.7738</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3868</v>
+        <v>0.4341</v>
       </c>
       <c r="J48" t="n">
-        <v>10.0568</v>
+        <v>11.2866</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.2628</v>
+        <v>-0.1671</v>
       </c>
       <c r="J49" t="n">
-        <v>-6.8328</v>
+        <v>-4.3446</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.68</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.5284</v>
+        <v>-0.3444</v>
       </c>
       <c r="J50" t="n">
-        <v>-13.7384</v>
+        <v>-8.9544</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.62</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.6062</v>
+        <v>-0.4007</v>
       </c>
       <c r="J51" t="n">
-        <v>-15.7612</v>
+        <v>-10.4182</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.6752</v>
+        <v>1.45</v>
       </c>
       <c r="J52" t="n">
-        <v>38.5296</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.7</v>
       </c>
       <c r="I53" t="n">
-        <v>1.4949</v>
+        <v>1.3346</v>
       </c>
       <c r="J53" t="n">
-        <v>34.3827</v>
+        <v>30.6958</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.35</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7443</v>
+        <v>0.8588</v>
       </c>
       <c r="J54" t="n">
-        <v>17.1189</v>
+        <v>19.7524</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.21</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4265</v>
+        <v>0.5358000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>9.8095</v>
+        <v>12.3234</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.15</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2815</v>
+        <v>0.3839</v>
       </c>
       <c r="J56" t="n">
-        <v>6.4745</v>
+        <v>8.829700000000001</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0697</v>
+        <v>0.0252</v>
       </c>
       <c r="J57" t="n">
-        <v>1.6031</v>
+        <v>0.5796</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.09669999999999999</v>
+        <v>-0.1046</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.2241</v>
+        <v>-2.4058</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3064</v>
+        <v>-0.2462</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.0472</v>
+        <v>-5.6626</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.43</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.7955</v>
+        <v>-0.5445</v>
       </c>
       <c r="J60" t="n">
-        <v>-18.2965</v>
+        <v>-12.5235</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.35</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8938</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>-20.5574</v>
+        <v>-14.2485</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0521</v>
+        <v>1.0216</v>
       </c>
       <c r="J62" t="n">
-        <v>28.4067</v>
+        <v>27.5832</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.587</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>15.849</v>
+        <v>15.147</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3264</v>
+        <v>0.3244</v>
       </c>
       <c r="J64" t="n">
-        <v>8.812799999999999</v>
+        <v>8.758800000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.96</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.252</v>
+        <v>-0.1882</v>
       </c>
       <c r="J65" t="n">
-        <v>-6.804</v>
+        <v>-5.0814</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6751</v>
+        <v>-0.621</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.2277</v>
+        <v>-16.767</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.65</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9188</v>
+        <v>1.1035</v>
       </c>
       <c r="J67" t="n">
-        <v>24.8076</v>
+        <v>29.7945</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2316</v>
+        <v>0.2585</v>
       </c>
       <c r="J68" t="n">
-        <v>6.2532</v>
+        <v>6.9795</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1277</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.4479</v>
+        <v>-1.7982</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4467</v>
+        <v>-0.2824</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.0609</v>
+        <v>-7.6248</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.539</v>
+        <v>-0.3494</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.553</v>
+        <v>-9.4338</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4044</v>
+        <v>0.4568</v>
       </c>
       <c r="J72" t="n">
-        <v>10.9188</v>
+        <v>12.3336</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0672</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.0088</v>
+        <v>-1.8144</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.95</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0672</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.0088</v>
+        <v>-1.8144</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.4724</v>
+        <v>-0.3053</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.7548</v>
+        <v>-8.2431</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4997</v>
+        <v>-0.3244</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.4919</v>
+        <v>-8.758800000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1182</v>
+        <v>1.0725</v>
       </c>
       <c r="J77" t="n">
-        <v>30.1914</v>
+        <v>28.9575</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5068</v>
+        <v>0.5174</v>
       </c>
       <c r="J78" t="n">
-        <v>13.6836</v>
+        <v>13.9698</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5068</v>
+        <v>0.5174</v>
       </c>
       <c r="J79" t="n">
-        <v>13.6836</v>
+        <v>13.9698</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3445</v>
+        <v>0.3923</v>
       </c>
       <c r="J80" t="n">
-        <v>9.301500000000001</v>
+        <v>10.5921</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4926</v>
+        <v>-0.4231</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.3002</v>
+        <v>-11.4237</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9467</v>
+        <v>0.9398</v>
       </c>
       <c r="J82" t="n">
-        <v>25.5609</v>
+        <v>25.3746</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8345</v>
+        <v>0.8269</v>
       </c>
       <c r="J83" t="n">
-        <v>22.5315</v>
+        <v>22.3263</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6917</v>
+        <v>0.6859</v>
       </c>
       <c r="J84" t="n">
-        <v>18.6759</v>
+        <v>18.5193</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3136</v>
+        <v>0.3653</v>
       </c>
       <c r="J85" t="n">
-        <v>8.4672</v>
+        <v>9.863099999999999</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.745</v>
+        <v>-0.6926</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.115</v>
+        <v>-18.7002</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.21</v>
       </c>
       <c r="I87" t="n">
-        <v>0.433</v>
+        <v>0.4949</v>
       </c>
       <c r="J87" t="n">
-        <v>11.691</v>
+        <v>13.3623</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.11</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2818</v>
+        <v>0.2975</v>
       </c>
       <c r="J88" t="n">
-        <v>7.6086</v>
+        <v>8.032500000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.293</v>
+        <v>-0.1868</v>
       </c>
       <c r="J89" t="n">
-        <v>-7.911</v>
+        <v>-5.0436</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.4158</v>
+        <v>-0.2666</v>
       </c>
       <c r="J90" t="n">
-        <v>-11.2266</v>
+        <v>-7.1982</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.6423</v>
+        <v>-0.4275</v>
       </c>
       <c r="J91" t="n">
-        <v>-17.3421</v>
+        <v>-11.5425</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4421</v>
+        <v>0.5102</v>
       </c>
       <c r="J92" t="n">
-        <v>12.8209</v>
+        <v>14.7958</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1549</v>
+        <v>0.15</v>
       </c>
       <c r="J93" t="n">
-        <v>4.4921</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.95</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.1106</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>-3.2074</v>
+        <v>-2.0851</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3114</v>
+        <v>-0.1929</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.0306</v>
+        <v>-5.5941</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5114</v>
+        <v>-0.3309</v>
       </c>
       <c r="J96" t="n">
-        <v>-14.8306</v>
+        <v>-9.5961</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.64</v>
       </c>
       <c r="I97" t="n">
-        <v>1.5125</v>
+        <v>1.3305</v>
       </c>
       <c r="J97" t="n">
-        <v>43.8625</v>
+        <v>38.5845</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7199</v>
+        <v>0.7114</v>
       </c>
       <c r="J98" t="n">
-        <v>20.8771</v>
+        <v>20.6306</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3177</v>
+        <v>0.3665</v>
       </c>
       <c r="J99" t="n">
-        <v>9.2133</v>
+        <v>10.6285</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.1076</v>
+        <v>-0.0384</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.1204</v>
+        <v>-1.1136</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.767</v>
+        <v>-0.7167</v>
       </c>
       <c r="J101" t="n">
-        <v>-22.243</v>
+        <v>-20.7843</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0032</v>
+        <v>-0.0377</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.9048</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.192</v>
+        <v>-0.1686</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.608</v>
+        <v>-4.0464</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.4709</v>
+        <v>-0.3246</v>
       </c>
       <c r="J104" t="n">
-        <v>-11.3016</v>
+        <v>-7.7904</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.64</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.5182</v>
+        <v>-0.3523</v>
       </c>
       <c r="J105" t="n">
-        <v>-12.4368</v>
+        <v>-8.4552</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8012</v>
+        <v>-0.5485</v>
       </c>
       <c r="J106" t="n">
-        <v>-19.2288</v>
+        <v>-13.164</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.648</v>
+        <v>1.4286</v>
       </c>
       <c r="J107" t="n">
-        <v>39.552</v>
+        <v>34.2864</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.55</v>
       </c>
       <c r="I108" t="n">
-        <v>1.2357</v>
+        <v>1.1675</v>
       </c>
       <c r="J108" t="n">
-        <v>29.6568</v>
+        <v>28.02</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.32</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7060999999999999</v>
+        <v>0.8044</v>
       </c>
       <c r="J109" t="n">
-        <v>16.9464</v>
+        <v>19.3056</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.26</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5659</v>
+        <v>0.6683</v>
       </c>
       <c r="J110" t="n">
-        <v>13.5816</v>
+        <v>16.0392</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.177</v>
+        <v>-0.0907</v>
       </c>
       <c r="J111" t="n">
-        <v>-4.248</v>
+        <v>-2.1768</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>1.6063</v>
+        <v>1.3997</v>
       </c>
       <c r="J112" t="n">
-        <v>36.9449</v>
+        <v>32.1931</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.53</v>
       </c>
       <c r="I113" t="n">
-        <v>1.2091</v>
+        <v>1.1478</v>
       </c>
       <c r="J113" t="n">
-        <v>27.8093</v>
+        <v>26.3994</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.4825</v>
+        <v>0.5792</v>
       </c>
       <c r="J114" t="n">
-        <v>11.0975</v>
+        <v>13.3216</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2837</v>
+        <v>0.3769</v>
       </c>
       <c r="J115" t="n">
-        <v>6.5251</v>
+        <v>8.668699999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.2578</v>
+        <v>0.3502</v>
       </c>
       <c r="J116" t="n">
-        <v>5.9294</v>
+        <v>8.054600000000001</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1637</v>
+        <v>-0.1513</v>
       </c>
       <c r="J117" t="n">
-        <v>-3.7651</v>
+        <v>-3.4799</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1637</v>
+        <v>-0.1513</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.7651</v>
+        <v>-3.4799</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.68</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.4289</v>
+        <v>-0.313</v>
       </c>
       <c r="J119" t="n">
-        <v>-9.864699999999999</v>
+        <v>-7.199</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.6792</v>
+        <v>-0.4604</v>
       </c>
       <c r="J120" t="n">
-        <v>-15.6216</v>
+        <v>-10.5892</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.6926</v>
+        <v>-0.4697</v>
       </c>
       <c r="J121" t="n">
-        <v>-15.9298</v>
+        <v>-10.8031</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4824</v>
+        <v>0.5798</v>
       </c>
       <c r="J122" t="n">
-        <v>14.472</v>
+        <v>17.394</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3428</v>
+        <v>0.4084</v>
       </c>
       <c r="J123" t="n">
-        <v>10.284</v>
+        <v>12.252</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3124</v>
+        <v>0.373</v>
       </c>
       <c r="J124" t="n">
-        <v>9.372</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.2472</v>
+        <v>0.3008</v>
       </c>
       <c r="J125" t="n">
-        <v>7.416</v>
+        <v>9.023999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4609</v>
+        <v>-0.291</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.827</v>
+        <v>-8.73</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.2905</v>
+        <v>0.3235</v>
       </c>
       <c r="J127" t="n">
-        <v>8.715</v>
+        <v>9.705</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2417</v>
+        <v>0.2646</v>
       </c>
       <c r="J128" t="n">
-        <v>7.251</v>
+        <v>7.938</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.97</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0959</v>
+        <v>-0.0507</v>
       </c>
       <c r="J129" t="n">
-        <v>-2.877</v>
+        <v>-1.521</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1179</v>
+        <v>-0.064</v>
       </c>
       <c r="J130" t="n">
-        <v>-3.537</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2956</v>
+        <v>-0.1784</v>
       </c>
       <c r="J131" t="n">
-        <v>-8.868</v>
+        <v>-5.352</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.04</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1526</v>
+        <v>0.1386</v>
       </c>
       <c r="J132" t="n">
-        <v>4.4254</v>
+        <v>4.0194</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>0.0137</v>
+        <v>-0.0115</v>
       </c>
       <c r="J133" t="n">
-        <v>0.3973</v>
+        <v>-0.3335</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.012</v>
+        <v>-0.0275</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.348</v>
+        <v>-0.7975</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2454</v>
+        <v>-0.1567</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.1166</v>
+        <v>-4.5443</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5416</v>
+        <v>-0.3539</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.7064</v>
+        <v>-10.2631</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7305</v>
+        <v>0.7168</v>
       </c>
       <c r="J137" t="n">
-        <v>21.1845</v>
+        <v>20.7872</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6817</v>
+        <v>0.6688</v>
       </c>
       <c r="J138" t="n">
-        <v>19.7693</v>
+        <v>19.3952</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.22</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6314</v>
+        <v>0.6203</v>
       </c>
       <c r="J139" t="n">
-        <v>18.3106</v>
+        <v>17.9887</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.16</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4673</v>
+        <v>0.4718</v>
       </c>
       <c r="J140" t="n">
-        <v>13.5517</v>
+        <v>13.6822</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.6064</v>
+        <v>-16.8809</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2855</v>
+        <v>0.2949</v>
       </c>
       <c r="J142" t="n">
-        <v>6.281</v>
+        <v>6.4878</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0887</v>
+        <v>-0.0931</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.9514</v>
+        <v>-2.0482</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.4417</v>
+        <v>-0.2965</v>
       </c>
       <c r="J144" t="n">
-        <v>-9.7174</v>
+        <v>-6.523</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.5159</v>
+        <v>-0.3437</v>
       </c>
       <c r="J145" t="n">
-        <v>-11.3498</v>
+        <v>-7.5614</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.48</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7529</v>
+        <v>-0.5115</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.5638</v>
+        <v>-11.253</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.61</v>
       </c>
       <c r="I147" t="n">
-        <v>1.3529</v>
+        <v>1.2396</v>
       </c>
       <c r="J147" t="n">
-        <v>29.7638</v>
+        <v>27.2712</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.58</v>
       </c>
       <c r="I148" t="n">
-        <v>1.2949</v>
+        <v>1.2036</v>
       </c>
       <c r="J148" t="n">
-        <v>28.4878</v>
+        <v>26.4792</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.35</v>
       </c>
       <c r="I149" t="n">
-        <v>0.7776</v>
+        <v>0.8697</v>
       </c>
       <c r="J149" t="n">
-        <v>17.1072</v>
+        <v>19.1334</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.4235</v>
+        <v>0.5243</v>
       </c>
       <c r="J150" t="n">
-        <v>9.317</v>
+        <v>11.5346</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>1.16</v>
       </c>
       <c r="I151" t="n">
-        <v>0.3252</v>
+        <v>0.4232</v>
       </c>
       <c r="J151" t="n">
-        <v>7.1544</v>
+        <v>9.3104</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.98</v>
       </c>
       <c r="I152" t="n">
-        <v>2.0451</v>
+        <v>1.7742</v>
       </c>
       <c r="J152" t="n">
-        <v>59.3079</v>
+        <v>51.4518</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1314</v>
+        <v>0.1752</v>
       </c>
       <c r="J153" t="n">
-        <v>3.8106</v>
+        <v>5.0808</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2237</v>
+        <v>-0.1575</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.4873</v>
+        <v>-4.5675</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3867</v>
+        <v>-0.3198</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.2143</v>
+        <v>-9.2742</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1266</v>
+        <v>-1.1181</v>
       </c>
       <c r="J156" t="n">
-        <v>-32.6714</v>
+        <v>-32.4249</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2725</v>
+        <v>0.295</v>
       </c>
       <c r="J157" t="n">
-        <v>7.9025</v>
+        <v>8.555</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1865</v>
+        <v>0.1908</v>
       </c>
       <c r="J158" t="n">
-        <v>5.4085</v>
+        <v>5.5332</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0716</v>
+        <v>-0.0478</v>
       </c>
       <c r="J159" t="n">
-        <v>-2.0764</v>
+        <v>-1.3862</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2846</v>
+        <v>-0.174</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.253399999999999</v>
+        <v>-5.046</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.83</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.3315</v>
+        <v>-0.2051</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.6135</v>
+        <v>-5.9479</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3791</v>
+        <v>1.2508</v>
       </c>
       <c r="J162" t="n">
-        <v>34.4775</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.5</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1629</v>
+        <v>1.1161</v>
       </c>
       <c r="J163" t="n">
-        <v>29.0725</v>
+        <v>27.9025</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.5446</v>
+        <v>0.6332</v>
       </c>
       <c r="J164" t="n">
-        <v>13.615</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.2</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4463</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="J165" t="n">
-        <v>11.1575</v>
+        <v>13.42</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.0713</v>
+        <v>0.1551</v>
       </c>
       <c r="J166" t="n">
-        <v>1.7825</v>
+        <v>3.8775</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0126</v>
+        <v>-0.0438</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.315</v>
+        <v>-1.095</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.84</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1857</v>
+        <v>-0.1623</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.6425</v>
+        <v>-4.0575</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.76</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3169</v>
+        <v>-0.2447</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.9225</v>
+        <v>-6.1175</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6524</v>
+        <v>-0.4396</v>
       </c>
       <c r="J170" t="n">
-        <v>-16.31</v>
+        <v>-10.99</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.52</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6919</v>
+        <v>-0.4676</v>
       </c>
       <c r="J171" t="n">
-        <v>-17.2975</v>
+        <v>-11.69</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.52</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.5545</v>
+        <v>-0.4266</v>
       </c>
       <c r="J172" t="n">
-        <v>-10.5355</v>
+        <v>-8.105399999999999</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.52</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.5545</v>
+        <v>-0.4266</v>
       </c>
       <c r="J173" t="n">
-        <v>-10.5355</v>
+        <v>-8.105399999999999</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.5</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.5919</v>
+        <v>-0.4448</v>
       </c>
       <c r="J174" t="n">
-        <v>-11.2461</v>
+        <v>-8.4512</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.47</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.4706</v>
       </c>
       <c r="J175" t="n">
-        <v>-12.5552</v>
+        <v>-8.9414</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.712</v>
+        <v>-0.4984</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.528</v>
+        <v>-9.4696</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2434</v>
+        <v>1.195</v>
       </c>
       <c r="J177" t="n">
-        <v>23.6246</v>
+        <v>22.705</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.58</v>
       </c>
       <c r="I178" t="n">
-        <v>1.2227</v>
+        <v>1.1835</v>
       </c>
       <c r="J178" t="n">
-        <v>23.2313</v>
+        <v>22.4865</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.57</v>
       </c>
       <c r="I179" t="n">
-        <v>1.2015</v>
+        <v>1.172</v>
       </c>
       <c r="J179" t="n">
-        <v>22.8285</v>
+        <v>22.268</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>0.9445</v>
+        <v>1.0438</v>
       </c>
       <c r="J180" t="n">
-        <v>17.9455</v>
+        <v>19.8322</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.44</v>
       </c>
       <c r="I181" t="n">
-        <v>0.9018</v>
+        <v>1.016</v>
       </c>
       <c r="J181" t="n">
-        <v>17.1342</v>
+        <v>19.304</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3647/event_3647_evp_summary.xlsx
+++ b/database/event/3647/event_3647_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2504</v>
+        <v>4.976</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0641</v>
+        <v>1.0084</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7323</v>
+        <v>1.641</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2504</v>
+        <v>4.976</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1303</v>
+        <v>2.8852</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1201</v>
+        <v>2.0908</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5139</v>
+        <v>3.5898</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8089</v>
+        <v>3.7772</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1201</v>
+        <v>2.0908</v>
       </c>
       <c r="K2" t="n">
         <v>114</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>5.929</v>
+        <v>5.868</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.4189</v>
+        <v>4.2014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8955</v>
+        <v>0.8515</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3569</v>
+        <v>1.2884</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4189</v>
+        <v>4.2014</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5585</v>
+        <v>3.3019</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8995</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4541</v>
+        <v>4.502</v>
       </c>
       <c r="I3" t="n">
-        <v>4.828</v>
+        <v>4.737</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.8995</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>5.688400000000001</v>
+        <v>5.6365</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.345</v>
+        <v>4.0811</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8806</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3235</v>
+        <v>1.2336</v>
       </c>
       <c r="E4" t="n">
-        <v>4.345</v>
+        <v>4.0811</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8723</v>
+        <v>2.6123</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4727</v>
+        <v>1.4688</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9474</v>
+        <v>2.9926</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1948</v>
+        <v>3.1488</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4727</v>
+        <v>1.4688</v>
       </c>
       <c r="K4" t="n">
         <v>114</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6675</v>
+        <v>4.6176</v>
       </c>
       <c r="N4" t="n">
         <v>193</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.2069</v>
+        <v>3.9271</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8526</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2612</v>
+        <v>1.1635</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2069</v>
+        <v>3.9271</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5766</v>
+        <v>3.2962</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6303</v>
+        <v>0.6309</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4938</v>
+        <v>4.4894</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8711</v>
+        <v>4.7238</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6303</v>
+        <v>0.6309</v>
       </c>
       <c r="K5" t="n">
         <v>114</v>
@@ -667,7 +667,7 @@
         <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>5.5014</v>
+        <v>5.354699999999999</v>
       </c>
       <c r="N5" t="n">
         <v>193</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.363</v>
+        <v>3.0296</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6816</v>
+        <v>0.614</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8802</v>
+        <v>0.7549</v>
       </c>
       <c r="E6" t="n">
-        <v>3.363</v>
+        <v>3.0296</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0564</v>
+        <v>2.7469</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3066</v>
+        <v>0.2827</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3515</v>
+        <v>3.2871</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3515</v>
+        <v>3.2871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3066</v>
+        <v>0.2827</v>
       </c>
       <c r="K6" t="n">
         <v>129</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6581</v>
+        <v>3.5698</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7481</v>
+        <v>2.5457</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5569</v>
+        <v>0.5159</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6026</v>
+        <v>0.5347</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7481</v>
+        <v>2.5457</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0674</v>
+        <v>2.8089</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3193</v>
+        <v>-0.2632</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3757</v>
+        <v>3.4229</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6591</v>
+        <v>3.6016</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3193</v>
+        <v>-0.2632</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3398</v>
+        <v>3.3384</v>
       </c>
       <c r="N7" t="n">
         <v>193</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5868</v>
+        <v>2.4472</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5242</v>
+        <v>0.496</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5298</v>
+        <v>0.4898</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5868</v>
+        <v>2.4472</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5868</v>
+        <v>2.4472</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5868</v>
+        <v>2.6312</v>
       </c>
       <c r="I8" t="n">
-        <v>2.5868</v>
+        <v>2.6312</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5868</v>
+        <v>2.6312</v>
       </c>
       <c r="N8" t="n">
         <v>128</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4529</v>
+        <v>0.4412</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3708</v>
+        <v>0.3667</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="I9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2347</v>
+        <v>2.1768</v>
       </c>
       <c r="N9" t="n">
         <v>139</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4094</v>
+        <v>0.3962</v>
       </c>
       <c r="D10" t="n">
-        <v>0.274</v>
+        <v>0.2657</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0201</v>
+        <v>1.9548</v>
       </c>
       <c r="N10" t="n">
         <v>139</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5757</v>
+        <v>1.4918</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3193</v>
+        <v>0.3023</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0733</v>
+        <v>0.0549</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5757</v>
+        <v>1.4918</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5002</v>
+        <v>1.4252</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0755</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5002</v>
+        <v>1.4252</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5002</v>
+        <v>1.4252</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0755</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="K11" t="n">
         <v>129</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5757</v>
+        <v>1.4918</v>
       </c>
       <c r="N11" t="n">
         <v>208</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.5525</v>
+        <v>1.425</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3146</v>
+        <v>0.2888</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0629</v>
+        <v>0.0245</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5525</v>
+        <v>1.425</v>
       </c>
       <c r="F12" t="n">
-        <v>2.0129</v>
+        <v>1.8831</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4604</v>
+        <v>-0.4581</v>
       </c>
       <c r="H12" t="n">
-        <v>2.0129</v>
+        <v>1.8831</v>
       </c>
       <c r="I12" t="n">
-        <v>2.0129</v>
+        <v>1.8831</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4604</v>
+        <v>-0.4581</v>
       </c>
       <c r="K12" t="n">
         <v>129</v>
@@ -989,7 +989,7 @@
         <v>79</v>
       </c>
       <c r="M12" t="n">
-        <v>1.5525</v>
+        <v>1.425</v>
       </c>
       <c r="N12" t="n">
         <v>208</v>
@@ -1002,28 +1002,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="C13" t="n">
-        <v>0.244</v>
+        <v>0.2626</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0946</v>
+        <v>-0.0344</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2038</v>
+        <v>1.2957</v>
       </c>
       <c r="N13" t="n">
         <v>139</v>
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="C14" t="n">
-        <v>0.167</v>
+        <v>0.1446</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2661</v>
+        <v>-0.2994</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8239</v>
+        <v>0.7135</v>
       </c>
       <c r="N14" t="n">
         <v>130</v>
@@ -1090,93 +1090,93 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>0.156</v>
+        <v>0.1407</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.2906</v>
+        <v>-0.3082</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7696</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1487</v>
+        <v>0.1392</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3068</v>
+        <v>-0.3115</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7336</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1465</v>
+        <v>0.1367</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3116</v>
+        <v>-0.3172</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7231</v>
+        <v>0.6744</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0859</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4467</v>
+        <v>-0.4777</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4237</v>
+        <v>0.3218</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3076</v>
+        <v>0.2841</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0623</v>
+        <v>0.0576</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4991</v>
+        <v>-0.4949</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3076</v>
+        <v>0.2841</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4985</v>
+        <v>0.5073</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1909</v>
+        <v>-0.2232</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4985</v>
+        <v>0.5073</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4985</v>
+        <v>0.5073</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1909</v>
+        <v>-0.2232</v>
       </c>
       <c r="K19" t="n">
         <v>129</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3076</v>
+        <v>0.2841</v>
       </c>
       <c r="N19" t="n">
         <v>208</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>flusha</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0118</v>
+        <v>-0.0061</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6642</v>
+        <v>-0.638</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0581</v>
+        <v>-0.0302</v>
       </c>
       <c r="N20" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>flusha</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0152</v>
+        <v>-0.0326</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.672</v>
+        <v>-0.6975</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0752</v>
+        <v>-0.1611</v>
       </c>
       <c r="N21" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0355</v>
+        <v>-0.0384</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.717</v>
+        <v>-0.7104</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.175</v>
+        <v>-0.1894</v>
       </c>
       <c r="N22" t="n">
         <v>130</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.062</v>
+        <v>-0.0825</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.7762</v>
+        <v>-0.8095</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.306</v>
+        <v>-0.4071</v>
       </c>
       <c r="N23" t="n">
         <v>128</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0725</v>
+        <v>-0.0858</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7996</v>
+        <v>-0.8169999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3579</v>
+        <v>-0.4236</v>
       </c>
       <c r="N24" t="n">
         <v>130</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0979</v>
+        <v>-0.1006</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8562</v>
+        <v>-0.8501</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4833</v>
+        <v>-0.4963</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1106</v>
+        <v>-0.1255</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.8844</v>
+        <v>-0.9062</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.5457</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6384</v>
+        <v>-0.6911</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1294</v>
+        <v>-0.1401</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9262</v>
+        <v>-0.9388</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6384</v>
+        <v>-0.6911</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2092</v>
+        <v>0.1936</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8476</v>
+        <v>-0.8847</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2092</v>
+        <v>0.1936</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2092</v>
+        <v>0.1936</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8476</v>
+        <v>-0.8847</v>
       </c>
       <c r="K27" t="n">
         <v>129</v>
@@ -1679,7 +1679,7 @@
         <v>79</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6384000000000001</v>
+        <v>-0.6911</v>
       </c>
       <c r="N27" t="n">
         <v>208</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1306</v>
+        <v>-0.1475</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9288</v>
+        <v>-0.9555</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.6442</v>
+        <v>-0.7277</v>
       </c>
       <c r="N28" t="n">
         <v>130</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1904</v>
+        <v>-0.1899</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0622</v>
+        <v>-1.0507</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9395</v>
+        <v>-0.9369</v>
       </c>
       <c r="N29" t="n">
         <v>128</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.1981</v>
+        <v>-0.2041</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0794</v>
+        <v>-1.0826</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.9777</v>
+        <v>-1.007</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3818</v>
+        <v>-0.3653</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.4885</v>
+        <v>-1.4448</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.8838</v>
+        <v>-1.8027</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8681</v>
+        <v>1.8453</v>
       </c>
       <c r="J2" t="n">
-        <v>35.4939</v>
+        <v>35.0607</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2123</v>
+        <v>1.2595</v>
       </c>
       <c r="J3" t="n">
-        <v>23.0337</v>
+        <v>23.9305</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2011</v>
+        <v>1.2432</v>
       </c>
       <c r="J4" t="n">
-        <v>22.8209</v>
+        <v>23.6208</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5795</v>
+        <v>0.578</v>
       </c>
       <c r="J5" t="n">
-        <v>11.0105</v>
+        <v>10.982</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8474</v>
+        <v>-0.7654</v>
       </c>
       <c r="J6" t="n">
-        <v>-16.1006</v>
+        <v>-14.5426</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2231</v>
+        <v>-0.2559</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.2389</v>
+        <v>-4.8621</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2458</v>
+        <v>-0.2772</v>
       </c>
       <c r="J8" t="n">
-        <v>-4.6702</v>
+        <v>-5.2668</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5121</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>-9.729900000000001</v>
+        <v>-10.0073</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.39</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5508</v>
+        <v>-0.5624</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.4652</v>
+        <v>-10.6856</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.64</v>
+        <v>-0.6438</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.16</v>
+        <v>-12.2322</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5018</v>
+        <v>0.4903</v>
       </c>
       <c r="J12" t="n">
-        <v>15.054</v>
+        <v>14.709</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0118</v>
+        <v>-0.0186</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.354</v>
+        <v>-0.5580000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0277</v>
+        <v>-0.0364</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.831</v>
+        <v>-1.092</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3352</v>
+        <v>-0.3486</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.056</v>
+        <v>-10.458</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4194</v>
+        <v>-0.4295</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.582</v>
+        <v>-12.885</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3648</v>
+        <v>0.3775</v>
       </c>
       <c r="J17" t="n">
-        <v>10.944</v>
+        <v>11.325</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2401</v>
+        <v>0.2561</v>
       </c>
       <c r="J18" t="n">
-        <v>7.203</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1749</v>
+        <v>0.1908</v>
       </c>
       <c r="J19" t="n">
-        <v>5.247</v>
+        <v>5.724</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1749</v>
+        <v>0.1908</v>
       </c>
       <c r="J20" t="n">
-        <v>5.247</v>
+        <v>5.724</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1003</v>
+        <v>-0.1085</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.009</v>
+        <v>-3.255</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6909999999999999</v>
+        <v>0.6551</v>
       </c>
       <c r="J22" t="n">
-        <v>20.73</v>
+        <v>19.653</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5399</v>
+        <v>0.5208</v>
       </c>
       <c r="J23" t="n">
-        <v>16.197</v>
+        <v>15.624</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0785</v>
+        <v>0.0893</v>
       </c>
       <c r="J24" t="n">
-        <v>2.355</v>
+        <v>2.679</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0167</v>
+        <v>-0.0114</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.501</v>
+        <v>-0.342</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2498</v>
+        <v>-0.2448</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.494</v>
+        <v>-7.344</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6825</v>
+        <v>0.6543</v>
       </c>
       <c r="J27" t="n">
-        <v>20.475</v>
+        <v>19.629</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1464</v>
+        <v>0.153</v>
       </c>
       <c r="J28" t="n">
-        <v>4.392</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0605</v>
+        <v>-0.0704</v>
       </c>
       <c r="J29" t="n">
-        <v>-1.815</v>
+        <v>-2.112</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2352</v>
+        <v>-0.2495</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.056</v>
+        <v>-7.485</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3326</v>
+        <v>-0.3448</v>
       </c>
       <c r="J31" t="n">
-        <v>-9.978</v>
+        <v>-10.344</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5238</v>
+        <v>0.4999</v>
       </c>
       <c r="J32" t="n">
-        <v>12.5712</v>
+        <v>11.9976</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4049</v>
+        <v>0.3902</v>
       </c>
       <c r="J33" t="n">
-        <v>9.717599999999999</v>
+        <v>9.364800000000001</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1611</v>
+        <v>-0.1784</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.8664</v>
+        <v>-4.2816</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3922</v>
+        <v>-0.4049</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.412800000000001</v>
+        <v>-9.717599999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6116</v>
+        <v>-0.6117</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.6784</v>
+        <v>-14.6808</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6826</v>
+        <v>1.6839</v>
       </c>
       <c r="J37" t="n">
-        <v>40.3824</v>
+        <v>40.4136</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2519</v>
+        <v>1.2297</v>
       </c>
       <c r="J38" t="n">
-        <v>30.0456</v>
+        <v>29.5128</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9502</v>
+        <v>0.9003</v>
       </c>
       <c r="J39" t="n">
-        <v>22.8048</v>
+        <v>21.6072</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1734</v>
+        <v>0.1997</v>
       </c>
       <c r="J40" t="n">
-        <v>4.1616</v>
+        <v>4.7928</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6615</v>
+        <v>-0.6061</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.876</v>
+        <v>-14.5464</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4777</v>
+        <v>1.4629</v>
       </c>
       <c r="J42" t="n">
-        <v>38.4202</v>
+        <v>38.0354</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.48</v>
       </c>
       <c r="I43" t="n">
-        <v>1.1068</v>
+        <v>1.0685</v>
       </c>
       <c r="J43" t="n">
-        <v>28.7768</v>
+        <v>27.781</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1425</v>
+        <v>0.1627</v>
       </c>
       <c r="J44" t="n">
-        <v>3.705</v>
+        <v>4.2302</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0585</v>
+        <v>-0.0405</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.521</v>
+        <v>-1.053</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.442</v>
+        <v>-0.4133</v>
       </c>
       <c r="J46" t="n">
-        <v>-11.492</v>
+        <v>-10.7458</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4913</v>
+        <v>0.4759</v>
       </c>
       <c r="J47" t="n">
-        <v>12.7738</v>
+        <v>12.3734</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4341</v>
+        <v>0.4231</v>
       </c>
       <c r="J48" t="n">
-        <v>11.2866</v>
+        <v>11.0006</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1671</v>
+        <v>-0.1829</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.3446</v>
+        <v>-4.7554</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.68</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3444</v>
+        <v>-0.3576</v>
       </c>
       <c r="J50" t="n">
-        <v>-8.9544</v>
+        <v>-9.297599999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.62</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4007</v>
+        <v>-0.4116</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.4182</v>
+        <v>-10.7016</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.45</v>
+        <v>1.4424</v>
       </c>
       <c r="J52" t="n">
-        <v>33.35</v>
+        <v>33.1752</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.7</v>
       </c>
       <c r="I53" t="n">
-        <v>1.3346</v>
+        <v>1.32</v>
       </c>
       <c r="J53" t="n">
-        <v>30.6958</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.35</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8588</v>
+        <v>0.8194</v>
       </c>
       <c r="J54" t="n">
-        <v>19.7524</v>
+        <v>18.8462</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.21</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5358000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J55" t="n">
-        <v>12.3234</v>
+        <v>12.2682</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.15</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3839</v>
+        <v>0.3966</v>
       </c>
       <c r="J56" t="n">
-        <v>8.829700000000001</v>
+        <v>9.1218</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0252</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5796</v>
+        <v>-0.1932</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1046</v>
+        <v>-0.1294</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.4058</v>
+        <v>-2.9762</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2462</v>
+        <v>-0.2684</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.6626</v>
+        <v>-6.1732</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.43</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5445</v>
+        <v>-0.5521</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.5235</v>
+        <v>-12.6983</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.35</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.6216</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.2485</v>
+        <v>-14.2968</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>1.0216</v>
+        <v>0.9603</v>
       </c>
       <c r="J62" t="n">
-        <v>27.5832</v>
+        <v>25.9281</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.5405</v>
       </c>
       <c r="J63" t="n">
-        <v>15.147</v>
+        <v>14.5935</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3244</v>
+        <v>0.3252</v>
       </c>
       <c r="J64" t="n">
-        <v>8.758800000000001</v>
+        <v>8.7804</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.96</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1882</v>
+        <v>-0.1852</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.0814</v>
+        <v>-5.0004</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.621</v>
+        <v>-0.5824</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.767</v>
+        <v>-15.7248</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.65</v>
       </c>
       <c r="I67" t="n">
-        <v>1.1035</v>
+        <v>1.0724</v>
       </c>
       <c r="J67" t="n">
-        <v>29.7945</v>
+        <v>28.9548</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2585</v>
+        <v>0.266</v>
       </c>
       <c r="J68" t="n">
-        <v>6.9795</v>
+        <v>7.182</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0751</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.7982</v>
+        <v>-2.0277</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2824</v>
+        <v>-0.2944</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.6248</v>
+        <v>-7.9488</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3494</v>
+        <v>-0.3598</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.4338</v>
+        <v>-9.714600000000001</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4568</v>
+        <v>0.4434</v>
       </c>
       <c r="J72" t="n">
-        <v>12.3336</v>
+        <v>11.9718</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0672</v>
+        <v>-0.0794</v>
       </c>
       <c r="J73" t="n">
-        <v>-1.8144</v>
+        <v>-2.1438</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.95</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0672</v>
+        <v>-0.0794</v>
       </c>
       <c r="J74" t="n">
-        <v>-1.8144</v>
+        <v>-2.1438</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3053</v>
+        <v>-0.3198</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.2431</v>
+        <v>-8.634600000000001</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3244</v>
+        <v>-0.3384</v>
       </c>
       <c r="J76" t="n">
-        <v>-8.758800000000001</v>
+        <v>-9.136799999999999</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0725</v>
+        <v>1.0255</v>
       </c>
       <c r="J77" t="n">
-        <v>28.9575</v>
+        <v>27.6885</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5174</v>
+        <v>0.5053</v>
       </c>
       <c r="J78" t="n">
-        <v>13.9698</v>
+        <v>13.6431</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5174</v>
+        <v>0.5053</v>
       </c>
       <c r="J79" t="n">
-        <v>13.9698</v>
+        <v>13.6431</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.3923</v>
+        <v>0.391</v>
       </c>
       <c r="J80" t="n">
-        <v>10.5921</v>
+        <v>10.557</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4231</v>
+        <v>-0.4001</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.4237</v>
+        <v>-10.8027</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.9398</v>
+        <v>0.8806</v>
       </c>
       <c r="J82" t="n">
-        <v>25.3746</v>
+        <v>23.7762</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.8269</v>
+        <v>0.7803</v>
       </c>
       <c r="J83" t="n">
-        <v>22.3263</v>
+        <v>21.0681</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6859</v>
+        <v>0.6562</v>
       </c>
       <c r="J84" t="n">
-        <v>18.5193</v>
+        <v>17.7174</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3653</v>
+        <v>0.3663</v>
       </c>
       <c r="J85" t="n">
-        <v>9.863099999999999</v>
+        <v>9.8901</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6926</v>
+        <v>-0.6424</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.7002</v>
+        <v>-17.3448</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.21</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4949</v>
+        <v>0.4785</v>
       </c>
       <c r="J87" t="n">
-        <v>13.3623</v>
+        <v>12.9195</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.11</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2975</v>
+        <v>0.2944</v>
       </c>
       <c r="J88" t="n">
-        <v>8.032500000000001</v>
+        <v>7.9488</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1868</v>
+        <v>-0.2029</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.0436</v>
+        <v>-5.4783</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2666</v>
+        <v>-0.282</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.1982</v>
+        <v>-7.614</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4275</v>
+        <v>-0.4374</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.5425</v>
+        <v>-11.8098</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5102</v>
+        <v>0.4966</v>
       </c>
       <c r="J92" t="n">
-        <v>14.7958</v>
+        <v>14.4014</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.15</v>
+        <v>0.1556</v>
       </c>
       <c r="J93" t="n">
-        <v>4.35</v>
+        <v>4.5124</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.95</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.083</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.0851</v>
+        <v>-2.407</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.1929</v>
+        <v>-0.2077</v>
       </c>
       <c r="J95" t="n">
-        <v>-5.5941</v>
+        <v>-6.0233</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3309</v>
+        <v>-0.3435</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.5961</v>
+        <v>-9.961499999999999</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.64</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3305</v>
+        <v>1.3036</v>
       </c>
       <c r="J97" t="n">
-        <v>38.5845</v>
+        <v>37.8044</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.7114</v>
+        <v>0.6784</v>
       </c>
       <c r="J98" t="n">
-        <v>20.6306</v>
+        <v>19.6736</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3665</v>
+        <v>0.3671</v>
       </c>
       <c r="J99" t="n">
-        <v>10.6285</v>
+        <v>10.6459</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0384</v>
+        <v>-0.0265</v>
       </c>
       <c r="J100" t="n">
-        <v>-1.1136</v>
+        <v>-0.7685</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.7167</v>
+        <v>-0.664</v>
       </c>
       <c r="J101" t="n">
-        <v>-20.7843</v>
+        <v>-19.256</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0377</v>
+        <v>-0.0598</v>
       </c>
       <c r="J102" t="n">
-        <v>-0.9048</v>
+        <v>-1.4352</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1686</v>
+        <v>-0.1913</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.0464</v>
+        <v>-4.5912</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3246</v>
+        <v>-0.3439</v>
       </c>
       <c r="J104" t="n">
-        <v>-7.7904</v>
+        <v>-8.2536</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.64</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3523</v>
+        <v>-0.3705</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.4552</v>
+        <v>-8.891999999999999</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5485</v>
+        <v>-0.5553</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.164</v>
+        <v>-13.3272</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4286</v>
+        <v>1.4174</v>
       </c>
       <c r="J107" t="n">
-        <v>34.2864</v>
+        <v>34.0176</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.55</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1675</v>
+        <v>1.1393</v>
       </c>
       <c r="J108" t="n">
-        <v>28.02</v>
+        <v>27.3432</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.32</v>
       </c>
       <c r="I109" t="n">
-        <v>0.8044</v>
+        <v>0.7693</v>
       </c>
       <c r="J109" t="n">
-        <v>19.3056</v>
+        <v>18.4632</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.26</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6683</v>
+        <v>0.6489</v>
       </c>
       <c r="J110" t="n">
-        <v>16.0392</v>
+        <v>15.5736</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.0907</v>
+        <v>-0.063</v>
       </c>
       <c r="J111" t="n">
-        <v>-2.1768</v>
+        <v>-1.512</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3997</v>
+        <v>1.3858</v>
       </c>
       <c r="J112" t="n">
-        <v>32.1931</v>
+        <v>31.8734</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.53</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1478</v>
+        <v>1.1172</v>
       </c>
       <c r="J113" t="n">
-        <v>26.3994</v>
+        <v>25.6956</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5792</v>
+        <v>0.5685</v>
       </c>
       <c r="J114" t="n">
-        <v>13.3216</v>
+        <v>13.0755</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3769</v>
+        <v>0.3862</v>
       </c>
       <c r="J115" t="n">
-        <v>8.668699999999999</v>
+        <v>8.8826</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3502</v>
+        <v>0.3618</v>
       </c>
       <c r="J116" t="n">
-        <v>8.054600000000001</v>
+        <v>8.321400000000001</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1513</v>
+        <v>-0.1755</v>
       </c>
       <c r="J117" t="n">
-        <v>-3.4799</v>
+        <v>-4.0365</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1513</v>
+        <v>-0.1755</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.4799</v>
+        <v>-4.0365</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.68</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.313</v>
+        <v>-0.3332</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.199</v>
+        <v>-7.6636</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4604</v>
+        <v>-0.4736</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.5892</v>
+        <v>-10.8928</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4697</v>
+        <v>-0.4824</v>
       </c>
       <c r="J121" t="n">
-        <v>-10.8031</v>
+        <v>-11.0952</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5798</v>
+        <v>0.57</v>
       </c>
       <c r="J122" t="n">
-        <v>17.394</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4084</v>
+        <v>0.4117</v>
       </c>
       <c r="J123" t="n">
-        <v>12.252</v>
+        <v>12.351</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.373</v>
+        <v>0.3785</v>
       </c>
       <c r="J124" t="n">
-        <v>11.19</v>
+        <v>11.355</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.3008</v>
+        <v>0.31</v>
       </c>
       <c r="J125" t="n">
-        <v>9.023999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.291</v>
+        <v>-0.3012</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.73</v>
+        <v>-9.036</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3235</v>
+        <v>0.3264</v>
       </c>
       <c r="J127" t="n">
-        <v>9.705</v>
+        <v>9.792</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2646</v>
+        <v>0.2704</v>
       </c>
       <c r="J128" t="n">
-        <v>7.938</v>
+        <v>8.112</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.97</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0507</v>
+        <v>-0.0587</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.521</v>
+        <v>-1.761</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.064</v>
+        <v>-0.0731</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.92</v>
+        <v>-2.193</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1784</v>
+        <v>-0.1916</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.352</v>
+        <v>-5.748</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.04</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1386</v>
+        <v>0.1409</v>
       </c>
       <c r="J132" t="n">
-        <v>4.0194</v>
+        <v>4.0861</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0115</v>
+        <v>-0.0183</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.3335</v>
+        <v>-0.5306999999999999</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0275</v>
+        <v>-0.0362</v>
       </c>
       <c r="J134" t="n">
-        <v>-0.7975</v>
+        <v>-1.0498</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1567</v>
+        <v>-0.1723</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.5443</v>
+        <v>-4.9967</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3539</v>
+        <v>-0.3667</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.2631</v>
+        <v>-10.6343</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.7168</v>
+        <v>0.6822</v>
       </c>
       <c r="J137" t="n">
-        <v>20.7872</v>
+        <v>19.7838</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6688</v>
+        <v>0.6397</v>
       </c>
       <c r="J138" t="n">
-        <v>19.3952</v>
+        <v>18.5513</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.22</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6203</v>
+        <v>0.5966</v>
       </c>
       <c r="J139" t="n">
-        <v>17.9887</v>
+        <v>17.3014</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.16</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4718</v>
+        <v>0.463</v>
       </c>
       <c r="J140" t="n">
-        <v>13.6822</v>
+        <v>13.427</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5821</v>
+        <v>-0.5451</v>
       </c>
       <c r="J141" t="n">
-        <v>-16.8809</v>
+        <v>-15.8079</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2949</v>
+        <v>0.2784</v>
       </c>
       <c r="J142" t="n">
-        <v>6.4878</v>
+        <v>6.1248</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0931</v>
+        <v>-0.1123</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.0482</v>
+        <v>-2.4706</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2965</v>
+        <v>-0.3149</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.523</v>
+        <v>-6.9278</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3437</v>
+        <v>-0.3604</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.5614</v>
+        <v>-7.9288</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.48</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5115</v>
+        <v>-0.5195</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.253</v>
+        <v>-11.429</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.61</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2396</v>
+        <v>1.2166</v>
       </c>
       <c r="J147" t="n">
-        <v>27.2712</v>
+        <v>26.7652</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.58</v>
       </c>
       <c r="I148" t="n">
-        <v>1.2036</v>
+        <v>1.1781</v>
       </c>
       <c r="J148" t="n">
-        <v>26.4792</v>
+        <v>25.9182</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.35</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8697</v>
+        <v>0.8268</v>
       </c>
       <c r="J149" t="n">
-        <v>19.1334</v>
+        <v>18.1896</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5243</v>
+        <v>0.5206</v>
       </c>
       <c r="J150" t="n">
-        <v>11.5346</v>
+        <v>11.4532</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>1.16</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4232</v>
+        <v>0.4295</v>
       </c>
       <c r="J151" t="n">
-        <v>9.3104</v>
+        <v>9.449</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.98</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7742</v>
+        <v>1.7639</v>
       </c>
       <c r="J152" t="n">
-        <v>51.4518</v>
+        <v>51.1531</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1752</v>
+        <v>0.1854</v>
       </c>
       <c r="J153" t="n">
-        <v>5.0808</v>
+        <v>5.3766</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1575</v>
+        <v>-0.1544</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.5675</v>
+        <v>-4.4776</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3198</v>
+        <v>-0.3083</v>
       </c>
       <c r="J155" t="n">
-        <v>-9.2742</v>
+        <v>-8.9407</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.1181</v>
+        <v>-1.0158</v>
       </c>
       <c r="J156" t="n">
-        <v>-32.4249</v>
+        <v>-29.4582</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.295</v>
+        <v>0.2971</v>
       </c>
       <c r="J157" t="n">
-        <v>8.555</v>
+        <v>8.6159</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1908</v>
+        <v>0.1968</v>
       </c>
       <c r="J158" t="n">
-        <v>5.5332</v>
+        <v>5.7072</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0478</v>
+        <v>-0.0565</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.3862</v>
+        <v>-1.6385</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.174</v>
+        <v>-0.1882</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.046</v>
+        <v>-5.4578</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.83</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2051</v>
+        <v>-0.2195</v>
       </c>
       <c r="J161" t="n">
-        <v>-5.9479</v>
+        <v>-6.3655</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2508</v>
+        <v>1.2265</v>
       </c>
       <c r="J162" t="n">
-        <v>31.27</v>
+        <v>30.6625</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.5</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1161</v>
+        <v>1.0819</v>
       </c>
       <c r="J163" t="n">
-        <v>27.9025</v>
+        <v>27.0475</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6332</v>
+        <v>0.6153999999999999</v>
       </c>
       <c r="J164" t="n">
-        <v>15.83</v>
+        <v>15.385</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.2</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.5293</v>
       </c>
       <c r="J165" t="n">
-        <v>13.42</v>
+        <v>13.2325</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1551</v>
+        <v>0.1794</v>
       </c>
       <c r="J166" t="n">
-        <v>3.8775</v>
+        <v>4.485</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0438</v>
+        <v>-0.0646</v>
       </c>
       <c r="J167" t="n">
-        <v>-1.095</v>
+        <v>-1.615</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.84</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1623</v>
+        <v>-0.1841</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.0575</v>
+        <v>-4.6025</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.76</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2447</v>
+        <v>-0.2652</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.1175</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4396</v>
+        <v>-0.4529</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.99</v>
+        <v>-11.3225</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.52</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4676</v>
+        <v>-0.4793</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.69</v>
+        <v>-11.9825</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.52</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.4266</v>
+        <v>-0.4475</v>
       </c>
       <c r="J172" t="n">
-        <v>-8.105399999999999</v>
+        <v>-8.5025</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.52</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4266</v>
+        <v>-0.4475</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.105399999999999</v>
+        <v>-8.5025</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.5</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4448</v>
+        <v>-0.4646</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.4512</v>
+        <v>-8.827400000000001</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.47</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4706</v>
+        <v>-0.4889</v>
       </c>
       <c r="J175" t="n">
-        <v>-8.9414</v>
+        <v>-9.289099999999999</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4984</v>
+        <v>-0.5147</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.4696</v>
+        <v>-9.779299999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.195</v>
+        <v>1.173</v>
       </c>
       <c r="J177" t="n">
-        <v>22.705</v>
+        <v>22.287</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.58</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1835</v>
+        <v>1.1606</v>
       </c>
       <c r="J178" t="n">
-        <v>22.4865</v>
+        <v>22.0514</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.57</v>
       </c>
       <c r="I179" t="n">
-        <v>1.172</v>
+        <v>1.1482</v>
       </c>
       <c r="J179" t="n">
-        <v>22.268</v>
+        <v>21.8158</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>1.0438</v>
+        <v>1.0042</v>
       </c>
       <c r="J180" t="n">
-        <v>19.8322</v>
+        <v>19.0798</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.44</v>
       </c>
       <c r="I181" t="n">
-        <v>1.016</v>
+        <v>0.9725</v>
       </c>
       <c r="J181" t="n">
-        <v>19.304</v>
+        <v>18.4775</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3647/event_3647_evp_summary.xlsx
+++ b/database/event/3647/event_3647_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.976</v>
+        <v>5.1049</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0084</v>
+        <v>1.0346</v>
       </c>
       <c r="D2" t="n">
-        <v>1.641</v>
+        <v>1.7197</v>
       </c>
       <c r="E2" t="n">
-        <v>4.976</v>
+        <v>5.1049</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8852</v>
+        <v>2.8265</v>
       </c>
       <c r="G2" t="n">
-        <v>2.0908</v>
+        <v>2.2784</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5898</v>
+        <v>3.5273</v>
       </c>
       <c r="I2" t="n">
-        <v>3.7772</v>
+        <v>3.7183</v>
       </c>
       <c r="J2" t="n">
-        <v>2.0908</v>
+        <v>2.2784</v>
       </c>
       <c r="K2" t="n">
         <v>114</v>
@@ -529,7 +529,7 @@
         <v>79</v>
       </c>
       <c r="M2" t="n">
-        <v>5.868</v>
+        <v>5.996700000000001</v>
       </c>
       <c r="N2" t="n">
         <v>193</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.2014</v>
+        <v>4.1955</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8515</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1.2884</v>
+        <v>1.3055</v>
       </c>
       <c r="E3" t="n">
-        <v>4.2014</v>
+        <v>4.1955</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3019</v>
+        <v>3.2439</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8995</v>
+        <v>0.9516</v>
       </c>
       <c r="H3" t="n">
-        <v>4.502</v>
+        <v>4.4839</v>
       </c>
       <c r="I3" t="n">
-        <v>4.737</v>
+        <v>4.7267</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8995</v>
+        <v>0.9516</v>
       </c>
       <c r="K3" t="n">
         <v>114</v>
@@ -575,7 +575,7 @@
         <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6365</v>
+        <v>5.6783</v>
       </c>
       <c r="N3" t="n">
         <v>193</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.0811</v>
+        <v>4.0241</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.8155</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2336</v>
+        <v>1.2274</v>
       </c>
       <c r="E4" t="n">
-        <v>4.0811</v>
+        <v>4.0241</v>
       </c>
       <c r="F4" t="n">
-        <v>2.6123</v>
+        <v>2.5517</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4688</v>
+        <v>1.4724</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9926</v>
+        <v>2.8976</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1488</v>
+        <v>3.0545</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4688</v>
+        <v>1.4724</v>
       </c>
       <c r="K4" t="n">
         <v>114</v>
@@ -621,7 +621,7 @@
         <v>79</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6176</v>
+        <v>4.526899999999999</v>
       </c>
       <c r="N4" t="n">
         <v>193</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.9271</v>
+        <v>3.8332</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.7768</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1635</v>
+        <v>1.1404</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9271</v>
+        <v>3.8332</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2962</v>
+        <v>3.2385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6309</v>
+        <v>0.5947</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4894</v>
+        <v>4.4716</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7238</v>
+        <v>4.7138</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6309</v>
+        <v>0.5947</v>
       </c>
       <c r="K5" t="n">
         <v>114</v>
@@ -667,7 +667,7 @@
         <v>79</v>
       </c>
       <c r="M5" t="n">
-        <v>5.354699999999999</v>
+        <v>5.3085</v>
       </c>
       <c r="N5" t="n">
         <v>193</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.0296</v>
+        <v>2.8868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.614</v>
+        <v>0.585</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7549</v>
+        <v>0.7093</v>
       </c>
       <c r="E6" t="n">
-        <v>3.0296</v>
+        <v>2.8868</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7469</v>
+        <v>2.708</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2827</v>
+        <v>0.1788</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2871</v>
+        <v>3.2558</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2871</v>
+        <v>3.2558</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2827</v>
+        <v>0.1788</v>
       </c>
       <c r="K6" t="n">
         <v>129</v>
@@ -713,7 +713,7 @@
         <v>79</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5698</v>
+        <v>3.4346</v>
       </c>
       <c r="N6" t="n">
         <v>208</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.5457</v>
+        <v>2.5174</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5159</v>
+        <v>0.5102</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5347</v>
+        <v>0.541</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5457</v>
+        <v>2.5174</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8089</v>
+        <v>2.8041</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2632</v>
+        <v>-0.2867</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4229</v>
+        <v>3.4759</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6016</v>
+        <v>3.6642</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2632</v>
+        <v>-0.2867</v>
       </c>
       <c r="K7" t="n">
         <v>114</v>
@@ -759,7 +759,7 @@
         <v>79</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3384</v>
+        <v>3.3775</v>
       </c>
       <c r="N7" t="n">
         <v>193</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4472</v>
+        <v>2.4645</v>
       </c>
       <c r="C8" t="n">
-        <v>0.496</v>
+        <v>0.4995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4898</v>
+        <v>0.5169</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4472</v>
+        <v>2.4645</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4472</v>
+        <v>2.4645</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.6312</v>
+        <v>2.6977</v>
       </c>
       <c r="I8" t="n">
-        <v>2.6312</v>
+        <v>2.6977</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6312</v>
+        <v>2.6977</v>
       </c>
       <c r="N8" t="n">
         <v>128</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4412</v>
+        <v>0.4205</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3667</v>
+        <v>0.3393</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.1768</v>
+        <v>2.0747</v>
       </c>
       <c r="N9" t="n">
         <v>139</v>
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="C10" t="n">
-        <v>0.3962</v>
+        <v>0.3684</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2657</v>
+        <v>0.2223</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="F10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9548</v>
+        <v>1.8178</v>
       </c>
       <c r="N10" t="n">
         <v>139</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.4918</v>
+        <v>1.498</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3023</v>
+        <v>0.3036</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0549</v>
+        <v>0.0766</v>
       </c>
       <c r="E11" t="n">
-        <v>1.4918</v>
+        <v>1.498</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4252</v>
+        <v>1.4929</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4252</v>
+        <v>1.4929</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4252</v>
+        <v>1.4929</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="K11" t="n">
         <v>129</v>
@@ -943,7 +943,7 @@
         <v>79</v>
       </c>
       <c r="M11" t="n">
-        <v>1.4918</v>
+        <v>1.498</v>
       </c>
       <c r="N11" t="n">
         <v>208</v>
@@ -952,231 +952,231 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>dennis</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.425</v>
+        <v>1.3431</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2888</v>
+        <v>0.2722</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0245</v>
+        <v>0.0061</v>
       </c>
       <c r="E12" t="n">
-        <v>1.425</v>
+        <v>1.3431</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8831</v>
+        <v>1.3431</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4581</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8831</v>
+        <v>1.3431</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8831</v>
+        <v>1.3431</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4581</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.425</v>
+        <v>1.3431</v>
       </c>
       <c r="N12" t="n">
-        <v>208</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dennis</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.2957</v>
+        <v>1.3391</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2626</v>
+        <v>0.2714</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0344</v>
+        <v>0.0042</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2957</v>
+        <v>1.3391</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2957</v>
+        <v>1.851</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.5119</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2957</v>
+        <v>1.851</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2957</v>
+        <v>1.851</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.5119</v>
       </c>
       <c r="K13" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2957</v>
+        <v>1.3391</v>
       </c>
       <c r="N13" t="n">
-        <v>139</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1446</v>
+        <v>0.15</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2994</v>
+        <v>-0.2686</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7135</v>
+        <v>0.7402</v>
       </c>
       <c r="N14" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>paz</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1407</v>
+        <v>0.1434</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3082</v>
+        <v>-0.2835</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6941000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="N15" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>paz</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1392</v>
+        <v>0.1401</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.3115</v>
+        <v>-0.2908</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6914</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1367</v>
+        <v>0.1103</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3172</v>
+        <v>-0.3578</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6744</v>
+        <v>0.5444</v>
       </c>
       <c r="N17" t="n">
         <v>130</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="C18" t="n">
-        <v>0.06519999999999999</v>
+        <v>0.0539</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4777</v>
+        <v>-0.4845</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3218</v>
+        <v>0.2662</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2841</v>
+        <v>0.2154</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0576</v>
+        <v>0.0437</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4949</v>
+        <v>-0.5077</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2841</v>
+        <v>0.2154</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5073</v>
+        <v>0.4678</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2232</v>
+        <v>-0.2524</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5073</v>
+        <v>0.4678</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5073</v>
+        <v>0.4678</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2232</v>
+        <v>-0.2524</v>
       </c>
       <c r="K19" t="n">
         <v>129</v>
@@ -1311,7 +1311,7 @@
         <v>79</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2841</v>
+        <v>0.2154</v>
       </c>
       <c r="N19" t="n">
         <v>208</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.0061</v>
+        <v>-0.0179</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.638</v>
+        <v>-0.646</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0302</v>
+        <v>-0.0882</v>
       </c>
       <c r="N20" t="n">
         <v>139</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0326</v>
+        <v>-0.0271</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6975</v>
+        <v>-0.6667</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1611</v>
+        <v>-0.1338</v>
       </c>
       <c r="N21" t="n">
         <v>128</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0384</v>
+        <v>-0.0516</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7104</v>
+        <v>-0.7218</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1894</v>
+        <v>-0.2547</v>
       </c>
       <c r="N22" t="n">
         <v>130</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0825</v>
+        <v>-0.0848</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8095</v>
+        <v>-0.7964</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4071</v>
+        <v>-0.4185</v>
       </c>
       <c r="N23" t="n">
         <v>128</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0858</v>
+        <v>-0.0954</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.8169999999999999</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4236</v>
+        <v>-0.4705</v>
       </c>
       <c r="N24" t="n">
         <v>130</v>
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.1006</v>
+        <v>-0.1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.8501</v>
+        <v>-0.8306</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.4963</v>
+        <v>-0.4935</v>
       </c>
       <c r="N25" t="n">
         <v>128</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.1255</v>
+        <v>-0.1201</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.9062</v>
+        <v>-0.8757</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-0.5924</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1642,124 +1642,124 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>pashaBiceps</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.6911</v>
+        <v>-0.7103</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.1401</v>
+        <v>-0.144</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.9388</v>
+        <v>-0.9294</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6911</v>
+        <v>-0.7103</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1936</v>
+        <v>-0.7103</v>
       </c>
       <c r="G27" t="n">
-        <v>-0.8847</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1936</v>
+        <v>-0.7103</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1936</v>
+        <v>-0.7103</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8847</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L27" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.6911</v>
+        <v>-0.7103</v>
       </c>
       <c r="N27" t="n">
-        <v>208</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>pashaBiceps</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.7277</v>
+        <v>-0.7168</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.1475</v>
+        <v>-0.1453</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.9555</v>
+        <v>-0.9323</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7277</v>
+        <v>-0.7168</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7277</v>
+        <v>0.1319</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>-0.8487</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7277</v>
+        <v>0.1319</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7277</v>
+        <v>0.1319</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-0.8487</v>
       </c>
       <c r="K28" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.7277</v>
+        <v>-0.7168</v>
       </c>
       <c r="N28" t="n">
-        <v>130</v>
+        <v>208</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>autimatic</t>
+          <t>ngiN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.1899</v>
+        <v>-0.1889</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.0507</v>
+        <v>-1.0303</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.9369</v>
+        <v>-0.9319</v>
       </c>
       <c r="N29" t="n">
         <v>128</v>
@@ -1780,32 +1780,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ngiN</t>
+          <t>autimatic</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.2041</v>
+        <v>-0.1991</v>
       </c>
       <c r="D30" t="n">
-        <v>-1.0826</v>
+        <v>-1.0533</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.007</v>
+        <v>-0.9823</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.3653</v>
+        <v>-0.3652</v>
       </c>
       <c r="D31" t="n">
-        <v>-1.4448</v>
+        <v>-1.4267</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-1.8027</v>
+        <v>-1.8021</v>
       </c>
       <c r="N31" t="n">
         <v>128</v>
@@ -1969,10 +1969,10 @@
         <v>2.72</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J2" t="n">
-        <v>35.0607</v>
+        <v>37.6618</v>
       </c>
     </row>
     <row r="3">
@@ -2009,10 +2009,10 @@
         <v>1.61</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2595</v>
+        <v>1.2926</v>
       </c>
       <c r="J3" t="n">
-        <v>23.9305</v>
+        <v>24.5594</v>
       </c>
     </row>
     <row r="4">
@@ -2049,10 +2049,10 @@
         <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2432</v>
+        <v>1.2746</v>
       </c>
       <c r="J4" t="n">
-        <v>23.6208</v>
+        <v>24.2174</v>
       </c>
     </row>
     <row r="5">
@@ -2089,10 +2089,10 @@
         <v>1.24</v>
       </c>
       <c r="I5" t="n">
-        <v>0.578</v>
+        <v>0.5526</v>
       </c>
       <c r="J5" t="n">
-        <v>10.982</v>
+        <v>10.4994</v>
       </c>
     </row>
     <row r="6">
@@ -2129,10 +2129,10 @@
         <v>0.76</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7654</v>
+        <v>-0.7534</v>
       </c>
       <c r="J6" t="n">
-        <v>-14.5426</v>
+        <v>-14.3146</v>
       </c>
     </row>
     <row r="7">
@@ -2169,10 +2169,10 @@
         <v>0.72</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2559</v>
+        <v>-0.2388</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.8621</v>
+        <v>-4.5372</v>
       </c>
     </row>
     <row r="8">
@@ -2209,10 +2209,10 @@
         <v>0.7</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2772</v>
+        <v>-0.2625</v>
       </c>
       <c r="J8" t="n">
-        <v>-5.2668</v>
+        <v>-4.9875</v>
       </c>
     </row>
     <row r="9">
@@ -2249,10 +2249,10 @@
         <v>0.43</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.5286</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.0073</v>
+        <v>-10.0434</v>
       </c>
     </row>
     <row r="10">
@@ -2289,10 +2289,10 @@
         <v>0.39</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5624</v>
+        <v>-0.5678</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.6856</v>
+        <v>-10.7882</v>
       </c>
     </row>
     <row r="11">
@@ -2329,10 +2329,10 @@
         <v>0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6438</v>
+        <v>-0.6613</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.2322</v>
+        <v>-12.5647</v>
       </c>
     </row>
     <row r="12">
@@ -2369,10 +2369,10 @@
         <v>1.3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4903</v>
+        <v>0.5024</v>
       </c>
       <c r="J12" t="n">
-        <v>14.709</v>
+        <v>15.072</v>
       </c>
     </row>
     <row r="13">
@@ -2409,10 +2409,10 @@
         <v>0.99</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0186</v>
+        <v>-0.0137</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.411</v>
       </c>
     </row>
     <row r="14">
@@ -2449,10 +2449,10 @@
         <v>0.98</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0364</v>
+        <v>-0.0285</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.092</v>
+        <v>-0.855</v>
       </c>
     </row>
     <row r="15">
@@ -2489,10 +2489,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3486</v>
+        <v>-0.3334</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.458</v>
+        <v>-10.002</v>
       </c>
     </row>
     <row r="16">
@@ -2529,10 +2529,10 @@
         <v>0.6</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4295</v>
+        <v>-0.4214</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.885</v>
+        <v>-12.642</v>
       </c>
     </row>
     <row r="17">
@@ -2569,10 +2569,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3775</v>
+        <v>0.3159</v>
       </c>
       <c r="J17" t="n">
-        <v>11.325</v>
+        <v>9.477</v>
       </c>
     </row>
     <row r="18">
@@ -2609,10 +2609,10 @@
         <v>1.16</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2561</v>
+        <v>0.2064</v>
       </c>
       <c r="J18" t="n">
-        <v>7.683</v>
+        <v>6.192</v>
       </c>
     </row>
     <row r="19">
@@ -2649,10 +2649,10 @@
         <v>1.11</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1908</v>
+        <v>0.15</v>
       </c>
       <c r="J19" t="n">
-        <v>5.724</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="20">
@@ -2689,10 +2689,10 @@
         <v>1.11</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1908</v>
+        <v>0.15</v>
       </c>
       <c r="J20" t="n">
-        <v>5.724</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="21">
@@ -2729,10 +2729,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1085</v>
+        <v>-0.0906</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.255</v>
+        <v>-2.718</v>
       </c>
     </row>
     <row r="22">
@@ -2769,10 +2769,10 @@
         <v>1.24</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6551</v>
+        <v>0.6192</v>
       </c>
       <c r="J22" t="n">
-        <v>19.653</v>
+        <v>18.576</v>
       </c>
     </row>
     <row r="23">
@@ -2809,10 +2809,10 @@
         <v>1.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5208</v>
+        <v>0.4804</v>
       </c>
       <c r="J23" t="n">
-        <v>15.624</v>
+        <v>14.412</v>
       </c>
     </row>
     <row r="24">
@@ -2849,10 +2849,10 @@
         <v>1.02</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0893</v>
+        <v>0.0706</v>
       </c>
       <c r="J24" t="n">
-        <v>2.679</v>
+        <v>2.118</v>
       </c>
     </row>
     <row r="25">
@@ -2889,10 +2889,10 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0114</v>
+        <v>-0.0076</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.342</v>
+        <v>-0.228</v>
       </c>
     </row>
     <row r="26">
@@ -2929,10 +2929,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.2448</v>
+        <v>-0.2062</v>
       </c>
       <c r="J26" t="n">
-        <v>-7.344</v>
+        <v>-6.186</v>
       </c>
     </row>
     <row r="27">
@@ -2969,10 +2969,10 @@
         <v>1.33</v>
       </c>
       <c r="I27" t="n">
-        <v>0.6543</v>
+        <v>0.5978</v>
       </c>
       <c r="J27" t="n">
-        <v>19.629</v>
+        <v>17.934</v>
       </c>
     </row>
     <row r="28">
@@ -3009,10 +3009,10 @@
         <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>0.153</v>
+        <v>0.1176</v>
       </c>
       <c r="J28" t="n">
-        <v>4.59</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="29">
@@ -3049,10 +3049,10 @@
         <v>0.96</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.0704</v>
+        <v>-0.057</v>
       </c>
       <c r="J29" t="n">
-        <v>-2.112</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="30">
@@ -3089,10 +3089,10 @@
         <v>0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2495</v>
+        <v>-0.2295</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.485</v>
+        <v>-6.885</v>
       </c>
     </row>
     <row r="31">
@@ -3129,10 +3129,10 @@
         <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3448</v>
+        <v>-0.3295</v>
       </c>
       <c r="J31" t="n">
-        <v>-10.344</v>
+        <v>-9.885</v>
       </c>
     </row>
     <row r="32">
@@ -3169,10 +3169,10 @@
         <v>1.21</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4999</v>
+        <v>0.4477</v>
       </c>
       <c r="J32" t="n">
-        <v>11.9976</v>
+        <v>10.7448</v>
       </c>
     </row>
     <row r="33">
@@ -3209,10 +3209,10 @@
         <v>1.15</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3902</v>
+        <v>0.3389</v>
       </c>
       <c r="J33" t="n">
-        <v>9.364800000000001</v>
+        <v>8.133599999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3249,10 +3249,10 @@
         <v>0.86</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1784</v>
+        <v>-0.1608</v>
       </c>
       <c r="J34" t="n">
-        <v>-4.2816</v>
+        <v>-3.8592</v>
       </c>
     </row>
     <row r="35">
@@ -3289,10 +3289,10 @@
         <v>0.62</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4049</v>
+        <v>-0.3939</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.717599999999999</v>
+        <v>-9.4536</v>
       </c>
     </row>
     <row r="36">
@@ -3329,10 +3329,10 @@
         <v>0.38</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6117</v>
+        <v>-0.6287</v>
       </c>
       <c r="J36" t="n">
-        <v>-14.6808</v>
+        <v>-15.0888</v>
       </c>
     </row>
     <row r="37">
@@ -3369,10 +3369,10 @@
         <v>1.99</v>
       </c>
       <c r="I37" t="n">
-        <v>1.6839</v>
+        <v>1.7319</v>
       </c>
       <c r="J37" t="n">
-        <v>40.4136</v>
+        <v>41.5656</v>
       </c>
     </row>
     <row r="38">
@@ -3409,10 +3409,10 @@
         <v>1.62</v>
       </c>
       <c r="I38" t="n">
-        <v>1.2297</v>
+        <v>1.2465</v>
       </c>
       <c r="J38" t="n">
-        <v>29.5128</v>
+        <v>29.916</v>
       </c>
     </row>
     <row r="39">
@@ -3449,10 +3449,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9003</v>
+        <v>0.8909</v>
       </c>
       <c r="J39" t="n">
-        <v>21.6072</v>
+        <v>21.3816</v>
       </c>
     </row>
     <row r="40">
@@ -3489,10 +3489,10 @@
         <v>1.07</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1997</v>
+        <v>0.1697</v>
       </c>
       <c r="J40" t="n">
-        <v>4.7928</v>
+        <v>4.0728</v>
       </c>
     </row>
     <row r="41">
@@ -3529,10 +3529,10 @@
         <v>0.82</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.6061</v>
+        <v>-0.5764</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.5464</v>
+        <v>-13.8336</v>
       </c>
     </row>
     <row r="42">
@@ -3569,10 +3569,10 @@
         <v>1.78</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4629</v>
+        <v>1.4942</v>
       </c>
       <c r="J42" t="n">
-        <v>38.0354</v>
+        <v>38.8492</v>
       </c>
     </row>
     <row r="43">
@@ -3609,10 +3609,10 @@
         <v>1.48</v>
       </c>
       <c r="I43" t="n">
-        <v>1.0685</v>
+        <v>1.0768</v>
       </c>
       <c r="J43" t="n">
-        <v>27.781</v>
+        <v>27.9968</v>
       </c>
     </row>
     <row r="44">
@@ -3649,10 +3649,10 @@
         <v>1.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1627</v>
+        <v>0.1368</v>
       </c>
       <c r="J44" t="n">
-        <v>4.2302</v>
+        <v>3.5568</v>
       </c>
     </row>
     <row r="45">
@@ -3689,10 +3689,10 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0405</v>
+        <v>-0.0351</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.053</v>
+        <v>-0.9126</v>
       </c>
     </row>
     <row r="46">
@@ -3729,10 +3729,10 @@
         <v>0.89</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4133</v>
+        <v>-0.3733</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.7458</v>
+        <v>-9.7058</v>
       </c>
     </row>
     <row r="47">
@@ -3769,10 +3769,10 @@
         <v>1.21</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4759</v>
+        <v>0.4196</v>
       </c>
       <c r="J47" t="n">
-        <v>12.3734</v>
+        <v>10.9096</v>
       </c>
     </row>
     <row r="48">
@@ -3809,10 +3809,10 @@
         <v>1.18</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4231</v>
+        <v>0.3676</v>
       </c>
       <c r="J48" t="n">
-        <v>11.0006</v>
+        <v>9.557600000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3849,10 +3849,10 @@
         <v>0.86</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.1829</v>
+        <v>-0.1634</v>
       </c>
       <c r="J49" t="n">
-        <v>-4.7554</v>
+        <v>-4.2484</v>
       </c>
     </row>
     <row r="50">
@@ -3889,10 +3889,10 @@
         <v>0.68</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.3576</v>
+        <v>-0.343</v>
       </c>
       <c r="J50" t="n">
-        <v>-9.297599999999999</v>
+        <v>-8.917999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3929,10 +3929,10 @@
         <v>0.62</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4116</v>
+        <v>-0.4017</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.7016</v>
+        <v>-10.4442</v>
       </c>
     </row>
     <row r="52">
@@ -3969,10 +3969,10 @@
         <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>1.4424</v>
+        <v>1.47</v>
       </c>
       <c r="J52" t="n">
-        <v>33.1752</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="53">
@@ -4009,10 +4009,10 @@
         <v>1.7</v>
       </c>
       <c r="I53" t="n">
-        <v>1.32</v>
+        <v>1.3412</v>
       </c>
       <c r="J53" t="n">
-        <v>30.36</v>
+        <v>30.8476</v>
       </c>
     </row>
     <row r="54">
@@ -4049,10 +4049,10 @@
         <v>1.35</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8194</v>
+        <v>0.8075</v>
       </c>
       <c r="J54" t="n">
-        <v>18.8462</v>
+        <v>18.5725</v>
       </c>
     </row>
     <row r="55">
@@ -4089,10 +4089,10 @@
         <v>1.21</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5334</v>
+        <v>0.5057</v>
       </c>
       <c r="J55" t="n">
-        <v>12.2682</v>
+        <v>11.6311</v>
       </c>
     </row>
     <row r="56">
@@ -4129,10 +4129,10 @@
         <v>1.15</v>
       </c>
       <c r="I56" t="n">
-        <v>0.3966</v>
+        <v>0.3647</v>
       </c>
       <c r="J56" t="n">
-        <v>9.1218</v>
+        <v>8.3881</v>
       </c>
     </row>
     <row r="57">
@@ -4169,10 +4169,10 @@
         <v>0.97</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0103</v>
       </c>
       <c r="J57" t="n">
-        <v>-0.1932</v>
+        <v>0.2369</v>
       </c>
     </row>
     <row r="58">
@@ -4209,10 +4209,10 @@
         <v>0.88</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1294</v>
+        <v>-0.1125</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.9762</v>
+        <v>-2.5875</v>
       </c>
     </row>
     <row r="59">
@@ -4249,10 +4249,10 @@
         <v>0.75</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2684</v>
+        <v>-0.2548</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.1732</v>
+        <v>-5.8604</v>
       </c>
     </row>
     <row r="60">
@@ -4289,10 +4289,10 @@
         <v>0.43</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5521</v>
+        <v>-0.5571</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.6983</v>
+        <v>-12.8133</v>
       </c>
     </row>
     <row r="61">
@@ -4329,10 +4329,10 @@
         <v>0.35</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6216</v>
+        <v>-0.6377</v>
       </c>
       <c r="J61" t="n">
-        <v>-14.2968</v>
+        <v>-14.6671</v>
       </c>
     </row>
     <row r="62">
@@ -4369,10 +4369,10 @@
         <v>1.39</v>
       </c>
       <c r="I62" t="n">
-        <v>0.9603</v>
+        <v>0.9505</v>
       </c>
       <c r="J62" t="n">
-        <v>25.9281</v>
+        <v>25.6635</v>
       </c>
     </row>
     <row r="63">
@@ -4409,10 +4409,10 @@
         <v>1.19</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5405</v>
+        <v>0.501</v>
       </c>
       <c r="J63" t="n">
-        <v>14.5935</v>
+        <v>13.527</v>
       </c>
     </row>
     <row r="64">
@@ -4449,10 +4449,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3252</v>
+        <v>0.2875</v>
       </c>
       <c r="J64" t="n">
-        <v>8.7804</v>
+        <v>7.7625</v>
       </c>
     </row>
     <row r="65">
@@ -4489,10 +4489,10 @@
         <v>0.96</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1852</v>
+        <v>-0.1509</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.0004</v>
+        <v>-4.0743</v>
       </c>
     </row>
     <row r="66">
@@ -4529,10 +4529,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5824</v>
+        <v>-0.5439000000000001</v>
       </c>
       <c r="J66" t="n">
-        <v>-15.7248</v>
+        <v>-14.6853</v>
       </c>
     </row>
     <row r="67">
@@ -4569,10 +4569,10 @@
         <v>1.65</v>
       </c>
       <c r="I67" t="n">
-        <v>1.0724</v>
+        <v>1.057</v>
       </c>
       <c r="J67" t="n">
-        <v>28.9548</v>
+        <v>28.539</v>
       </c>
     </row>
     <row r="68">
@@ -4609,10 +4609,10 @@
         <v>1.11</v>
       </c>
       <c r="I68" t="n">
-        <v>0.266</v>
+        <v>0.2189</v>
       </c>
       <c r="J68" t="n">
-        <v>7.182</v>
+        <v>5.9103</v>
       </c>
     </row>
     <row r="69">
@@ -4649,10 +4649,10 @@
         <v>0.96</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0751</v>
+        <v>-0.0602</v>
       </c>
       <c r="J69" t="n">
-        <v>-2.0277</v>
+        <v>-1.6254</v>
       </c>
     </row>
     <row r="70">
@@ -4689,10 +4689,10 @@
         <v>0.76</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.2944</v>
+        <v>-0.2764</v>
       </c>
       <c r="J70" t="n">
-        <v>-7.9488</v>
+        <v>-7.4628</v>
       </c>
     </row>
     <row r="71">
@@ -4729,10 +4729,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3598</v>
+        <v>-0.3462</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.714600000000001</v>
+        <v>-9.3474</v>
       </c>
     </row>
     <row r="72">
@@ -4769,10 +4769,10 @@
         <v>1.19</v>
       </c>
       <c r="I72" t="n">
-        <v>0.4434</v>
+        <v>0.3879</v>
       </c>
       <c r="J72" t="n">
-        <v>11.9718</v>
+        <v>10.4733</v>
       </c>
     </row>
     <row r="73">
@@ -4809,10 +4809,10 @@
         <v>0.95</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.0794</v>
+        <v>-0.0664</v>
       </c>
       <c r="J73" t="n">
-        <v>-2.1438</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="74">
@@ -4849,10 +4849,10 @@
         <v>0.95</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.0794</v>
+        <v>-0.0664</v>
       </c>
       <c r="J74" t="n">
-        <v>-2.1438</v>
+        <v>-1.7928</v>
       </c>
     </row>
     <row r="75">
@@ -4889,10 +4889,10 @@
         <v>0.72</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.3198</v>
+        <v>-0.3028</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.634600000000001</v>
+        <v>-8.175599999999999</v>
       </c>
     </row>
     <row r="76">
@@ -4929,10 +4929,10 @@
         <v>0.7</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.3384</v>
+        <v>-0.3224</v>
       </c>
       <c r="J76" t="n">
-        <v>-9.136799999999999</v>
+        <v>-8.704800000000001</v>
       </c>
     </row>
     <row r="77">
@@ -4969,10 +4969,10 @@
         <v>1.44</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0255</v>
+        <v>1.0268</v>
       </c>
       <c r="J77" t="n">
-        <v>27.6885</v>
+        <v>27.7236</v>
       </c>
     </row>
     <row r="78">
@@ -5009,10 +5009,10 @@
         <v>1.18</v>
       </c>
       <c r="I78" t="n">
-        <v>0.5053</v>
+        <v>0.4689</v>
       </c>
       <c r="J78" t="n">
-        <v>13.6431</v>
+        <v>12.6603</v>
       </c>
     </row>
     <row r="79">
@@ -5049,10 +5049,10 @@
         <v>1.18</v>
       </c>
       <c r="I79" t="n">
-        <v>0.5053</v>
+        <v>0.4689</v>
       </c>
       <c r="J79" t="n">
-        <v>13.6431</v>
+        <v>12.6603</v>
       </c>
     </row>
     <row r="80">
@@ -5089,10 +5089,10 @@
         <v>1.13</v>
       </c>
       <c r="I80" t="n">
-        <v>0.391</v>
+        <v>0.3553</v>
       </c>
       <c r="J80" t="n">
-        <v>10.557</v>
+        <v>9.5931</v>
       </c>
     </row>
     <row r="81">
@@ -5129,10 +5129,10 @@
         <v>0.89</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4001</v>
+        <v>-0.3582</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.8027</v>
+        <v>-9.6714</v>
       </c>
     </row>
     <row r="82">
@@ -5169,10 +5169,10 @@
         <v>1.36</v>
       </c>
       <c r="I82" t="n">
-        <v>0.8806</v>
+        <v>0.8612</v>
       </c>
       <c r="J82" t="n">
-        <v>23.7762</v>
+        <v>23.2524</v>
       </c>
     </row>
     <row r="83">
@@ -5209,10 +5209,10 @@
         <v>1.31</v>
       </c>
       <c r="I83" t="n">
-        <v>0.7803</v>
+        <v>0.7536</v>
       </c>
       <c r="J83" t="n">
-        <v>21.0681</v>
+        <v>20.3472</v>
       </c>
     </row>
     <row r="84">
@@ -5249,10 +5249,10 @@
         <v>1.25</v>
       </c>
       <c r="I84" t="n">
-        <v>0.6562</v>
+        <v>0.6231</v>
       </c>
       <c r="J84" t="n">
-        <v>17.7174</v>
+        <v>16.8237</v>
       </c>
     </row>
     <row r="85">
@@ -5289,10 +5289,10 @@
         <v>1.12</v>
       </c>
       <c r="I85" t="n">
-        <v>0.3663</v>
+        <v>0.3311</v>
       </c>
       <c r="J85" t="n">
-        <v>9.8901</v>
+        <v>8.9397</v>
       </c>
     </row>
     <row r="86">
@@ -5329,10 +5329,10 @@
         <v>0.79</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6424</v>
+        <v>-0.6087</v>
       </c>
       <c r="J86" t="n">
-        <v>-17.3448</v>
+        <v>-16.4349</v>
       </c>
     </row>
     <row r="87">
@@ -5369,10 +5369,10 @@
         <v>1.21</v>
       </c>
       <c r="I87" t="n">
-        <v>0.4785</v>
+        <v>0.4226</v>
       </c>
       <c r="J87" t="n">
-        <v>12.9195</v>
+        <v>11.4102</v>
       </c>
     </row>
     <row r="88">
@@ -5409,10 +5409,10 @@
         <v>1.11</v>
       </c>
       <c r="I88" t="n">
-        <v>0.2944</v>
+        <v>0.2449</v>
       </c>
       <c r="J88" t="n">
-        <v>7.9488</v>
+        <v>6.6123</v>
       </c>
     </row>
     <row r="89">
@@ -5449,10 +5449,10 @@
         <v>0.84</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2029</v>
+        <v>-0.1832</v>
       </c>
       <c r="J89" t="n">
-        <v>-5.4783</v>
+        <v>-4.9464</v>
       </c>
     </row>
     <row r="90">
@@ -5489,10 +5489,10 @@
         <v>0.76</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.282</v>
+        <v>-0.2632</v>
       </c>
       <c r="J90" t="n">
-        <v>-7.614</v>
+        <v>-7.1064</v>
       </c>
     </row>
     <row r="91">
@@ -5529,10 +5529,10 @@
         <v>0.59</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4374</v>
+        <v>-0.43</v>
       </c>
       <c r="J91" t="n">
-        <v>-11.8098</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="92">
@@ -5569,10 +5569,10 @@
         <v>1.23</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4966</v>
+        <v>0.4385</v>
       </c>
       <c r="J92" t="n">
-        <v>14.4014</v>
+        <v>12.7165</v>
       </c>
     </row>
     <row r="93">
@@ -5609,10 +5609,10 @@
         <v>1.05</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1556</v>
+        <v>0.1197</v>
       </c>
       <c r="J93" t="n">
-        <v>4.5124</v>
+        <v>3.4713</v>
       </c>
     </row>
     <row r="94">
@@ -5649,10 +5649,10 @@
         <v>0.95</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.083</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>-2.407</v>
+        <v>-1.9865</v>
       </c>
     </row>
     <row r="95">
@@ -5689,10 +5689,10 @@
         <v>0.84</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2077</v>
+        <v>-0.1873</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.0233</v>
+        <v>-5.4317</v>
       </c>
     </row>
     <row r="96">
@@ -5729,10 +5729,10 @@
         <v>0.7</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3435</v>
+        <v>-0.328</v>
       </c>
       <c r="J96" t="n">
-        <v>-9.961499999999999</v>
+        <v>-9.512</v>
       </c>
     </row>
     <row r="97">
@@ -5769,10 +5769,10 @@
         <v>1.64</v>
       </c>
       <c r="I97" t="n">
-        <v>1.3036</v>
+        <v>1.3254</v>
       </c>
       <c r="J97" t="n">
-        <v>37.8044</v>
+        <v>38.4366</v>
       </c>
     </row>
     <row r="98">
@@ -5809,10 +5809,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6784</v>
+        <v>0.646</v>
       </c>
       <c r="J98" t="n">
-        <v>19.6736</v>
+        <v>18.734</v>
       </c>
     </row>
     <row r="99">
@@ -5849,10 +5849,10 @@
         <v>1.12</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3671</v>
+        <v>0.3317</v>
       </c>
       <c r="J99" t="n">
-        <v>10.6459</v>
+        <v>9.619300000000001</v>
       </c>
     </row>
     <row r="100">
@@ -5889,10 +5889,10 @@
         <v>1</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0265</v>
+        <v>-0.021</v>
       </c>
       <c r="J100" t="n">
-        <v>-0.7685</v>
+        <v>-0.609</v>
       </c>
     </row>
     <row r="101">
@@ -5929,10 +5929,10 @@
         <v>0.78</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.664</v>
+        <v>-0.6316000000000001</v>
       </c>
       <c r="J101" t="n">
-        <v>-19.256</v>
+        <v>-18.3164</v>
       </c>
     </row>
     <row r="102">
@@ -5969,10 +5969,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I102" t="n">
-        <v>-0.0598</v>
+        <v>-0.0447</v>
       </c>
       <c r="J102" t="n">
-        <v>-1.4352</v>
+        <v>-1.0728</v>
       </c>
     </row>
     <row r="103">
@@ -6009,10 +6009,10 @@
         <v>0.83</v>
       </c>
       <c r="I103" t="n">
-        <v>-0.1913</v>
+        <v>-0.1758</v>
       </c>
       <c r="J103" t="n">
-        <v>-4.5912</v>
+        <v>-4.2192</v>
       </c>
     </row>
     <row r="104">
@@ -6049,10 +6049,10 @@
         <v>0.67</v>
       </c>
       <c r="I104" t="n">
-        <v>-0.3439</v>
+        <v>-0.3305</v>
       </c>
       <c r="J104" t="n">
-        <v>-8.2536</v>
+        <v>-7.932</v>
       </c>
     </row>
     <row r="105">
@@ -6089,10 +6089,10 @@
         <v>0.64</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.3705</v>
+        <v>-0.3581</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.891999999999999</v>
+        <v>-8.5944</v>
       </c>
     </row>
     <row r="106">
@@ -6129,10 +6129,10 @@
         <v>0.43</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5553</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J106" t="n">
-        <v>-13.3272</v>
+        <v>-13.464</v>
       </c>
     </row>
     <row r="107">
@@ -6169,10 +6169,10 @@
         <v>1.77</v>
       </c>
       <c r="I107" t="n">
-        <v>1.4174</v>
+        <v>1.4433</v>
       </c>
       <c r="J107" t="n">
-        <v>34.0176</v>
+        <v>34.6392</v>
       </c>
     </row>
     <row r="108">
@@ -6209,10 +6209,10 @@
         <v>1.55</v>
       </c>
       <c r="I108" t="n">
-        <v>1.1393</v>
+        <v>1.1539</v>
       </c>
       <c r="J108" t="n">
-        <v>27.3432</v>
+        <v>27.6936</v>
       </c>
     </row>
     <row r="109">
@@ -6249,10 +6249,10 @@
         <v>1.32</v>
       </c>
       <c r="I109" t="n">
-        <v>0.7693</v>
+        <v>0.7519</v>
       </c>
       <c r="J109" t="n">
-        <v>18.4632</v>
+        <v>18.0456</v>
       </c>
     </row>
     <row r="110">
@@ -6289,10 +6289,10 @@
         <v>1.26</v>
       </c>
       <c r="I110" t="n">
-        <v>0.6489</v>
+        <v>0.6253</v>
       </c>
       <c r="J110" t="n">
-        <v>15.5736</v>
+        <v>15.0072</v>
       </c>
     </row>
     <row r="111">
@@ -6329,10 +6329,10 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.063</v>
+        <v>-0.0601</v>
       </c>
       <c r="J111" t="n">
-        <v>-1.512</v>
+        <v>-1.4424</v>
       </c>
     </row>
     <row r="112">
@@ -6369,10 +6369,10 @@
         <v>1.74</v>
       </c>
       <c r="I112" t="n">
-        <v>1.3858</v>
+        <v>1.4098</v>
       </c>
       <c r="J112" t="n">
-        <v>31.8734</v>
+        <v>32.4254</v>
       </c>
     </row>
     <row r="113">
@@ -6409,10 +6409,10 @@
         <v>1.53</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1172</v>
+        <v>1.1308</v>
       </c>
       <c r="J113" t="n">
-        <v>25.6956</v>
+        <v>26.0084</v>
       </c>
     </row>
     <row r="114">
@@ -6449,10 +6449,10 @@
         <v>1.22</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5685</v>
+        <v>0.5409</v>
       </c>
       <c r="J114" t="n">
-        <v>13.0755</v>
+        <v>12.4407</v>
       </c>
     </row>
     <row r="115">
@@ -6489,10 +6489,10 @@
         <v>1.14</v>
       </c>
       <c r="I115" t="n">
-        <v>0.3862</v>
+        <v>0.3544</v>
       </c>
       <c r="J115" t="n">
-        <v>8.8826</v>
+        <v>8.151199999999999</v>
       </c>
     </row>
     <row r="116">
@@ -6529,10 +6529,10 @@
         <v>1.13</v>
       </c>
       <c r="I116" t="n">
-        <v>0.3618</v>
+        <v>0.3299</v>
       </c>
       <c r="J116" t="n">
-        <v>8.321400000000001</v>
+        <v>7.5877</v>
       </c>
     </row>
     <row r="117">
@@ -6569,10 +6569,10 @@
         <v>0.84</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.1755</v>
+        <v>-0.1596</v>
       </c>
       <c r="J117" t="n">
-        <v>-4.0365</v>
+        <v>-3.6708</v>
       </c>
     </row>
     <row r="118">
@@ -6609,10 +6609,10 @@
         <v>0.84</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1755</v>
+        <v>-0.1596</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.0365</v>
+        <v>-3.6708</v>
       </c>
     </row>
     <row r="119">
@@ -6649,10 +6649,10 @@
         <v>0.68</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.3332</v>
+        <v>-0.3205</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.6636</v>
+        <v>-7.3715</v>
       </c>
     </row>
     <row r="120">
@@ -6689,10 +6689,10 @@
         <v>0.52</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4736</v>
+        <v>-0.4689</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.8928</v>
+        <v>-10.7847</v>
       </c>
     </row>
     <row r="121">
@@ -6729,10 +6729,10 @@
         <v>0.51</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4824</v>
+        <v>-0.4786</v>
       </c>
       <c r="J121" t="n">
-        <v>-11.0952</v>
+        <v>-11.0078</v>
       </c>
     </row>
     <row r="122">
@@ -6769,10 +6769,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.57</v>
+        <v>0.5104</v>
       </c>
       <c r="J122" t="n">
-        <v>17.1</v>
+        <v>15.312</v>
       </c>
     </row>
     <row r="123">
@@ -6809,10 +6809,10 @@
         <v>1.2</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4117</v>
+        <v>0.3565</v>
       </c>
       <c r="J123" t="n">
-        <v>12.351</v>
+        <v>10.695</v>
       </c>
     </row>
     <row r="124">
@@ -6849,10 +6849,10 @@
         <v>1.18</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3785</v>
+        <v>0.3252</v>
       </c>
       <c r="J124" t="n">
-        <v>11.355</v>
+        <v>9.756</v>
       </c>
     </row>
     <row r="125">
@@ -6889,10 +6889,10 @@
         <v>1.14</v>
       </c>
       <c r="I125" t="n">
-        <v>0.31</v>
+        <v>0.2616</v>
       </c>
       <c r="J125" t="n">
-        <v>9.300000000000001</v>
+        <v>7.848</v>
       </c>
     </row>
     <row r="126">
@@ -6929,10 +6929,10 @@
         <v>0.76</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3012</v>
+        <v>-0.2843</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.036</v>
+        <v>-8.529</v>
       </c>
     </row>
     <row r="127">
@@ -6969,10 +6969,10 @@
         <v>1.14</v>
       </c>
       <c r="I127" t="n">
-        <v>0.3264</v>
+        <v>0.2741</v>
       </c>
       <c r="J127" t="n">
-        <v>9.792</v>
+        <v>8.223000000000001</v>
       </c>
     </row>
     <row r="128">
@@ -7009,10 +7009,10 @@
         <v>1.11</v>
       </c>
       <c r="I128" t="n">
-        <v>0.2704</v>
+        <v>0.2224</v>
       </c>
       <c r="J128" t="n">
-        <v>8.112</v>
+        <v>6.672</v>
       </c>
     </row>
     <row r="129">
@@ -7049,10 +7049,10 @@
         <v>0.97</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.0587</v>
+        <v>-0.046</v>
       </c>
       <c r="J129" t="n">
-        <v>-1.761</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="130">
@@ -7089,10 +7089,10 @@
         <v>0.96</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0731</v>
+        <v>-0.0586</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.193</v>
+        <v>-1.758</v>
       </c>
     </row>
     <row r="131">
@@ -7129,10 +7129,10 @@
         <v>0.86</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1916</v>
+        <v>-0.171</v>
       </c>
       <c r="J131" t="n">
-        <v>-5.748</v>
+        <v>-5.13</v>
       </c>
     </row>
     <row r="132">
@@ -7169,10 +7169,10 @@
         <v>1.04</v>
       </c>
       <c r="I132" t="n">
-        <v>0.1409</v>
+        <v>0.1072</v>
       </c>
       <c r="J132" t="n">
-        <v>4.0861</v>
+        <v>3.1088</v>
       </c>
     </row>
     <row r="133">
@@ -7209,10 +7209,10 @@
         <v>0.99</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0183</v>
+        <v>-0.0135</v>
       </c>
       <c r="J133" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.3915</v>
       </c>
     </row>
     <row r="134">
@@ -7249,10 +7249,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.0362</v>
+        <v>-0.0283</v>
       </c>
       <c r="J134" t="n">
-        <v>-1.0498</v>
+        <v>-0.8207</v>
       </c>
     </row>
     <row r="135">
@@ -7289,10 +7289,10 @@
         <v>0.87</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1723</v>
+        <v>-0.1531</v>
       </c>
       <c r="J135" t="n">
-        <v>-4.9967</v>
+        <v>-4.4399</v>
       </c>
     </row>
     <row r="136">
@@ -7329,10 +7329,10 @@
         <v>0.67</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3667</v>
+        <v>-0.3528</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6343</v>
+        <v>-10.2312</v>
       </c>
     </row>
     <row r="137">
@@ -7369,10 +7369,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6822</v>
+        <v>0.6492</v>
       </c>
       <c r="J137" t="n">
-        <v>19.7838</v>
+        <v>18.8268</v>
       </c>
     </row>
     <row r="138">
@@ -7409,10 +7409,10 @@
         <v>1.24</v>
       </c>
       <c r="I138" t="n">
-        <v>0.6397</v>
+        <v>0.605</v>
       </c>
       <c r="J138" t="n">
-        <v>18.5513</v>
+        <v>17.545</v>
       </c>
     </row>
     <row r="139">
@@ -7449,10 +7449,10 @@
         <v>1.22</v>
       </c>
       <c r="I139" t="n">
-        <v>0.5966</v>
+        <v>0.5605</v>
       </c>
       <c r="J139" t="n">
-        <v>17.3014</v>
+        <v>16.2545</v>
       </c>
     </row>
     <row r="140">
@@ -7489,10 +7489,10 @@
         <v>1.16</v>
       </c>
       <c r="I140" t="n">
-        <v>0.463</v>
+        <v>0.4253</v>
       </c>
       <c r="J140" t="n">
-        <v>13.427</v>
+        <v>12.3337</v>
       </c>
     </row>
     <row r="141">
@@ -7529,10 +7529,10 @@
         <v>0.83</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5451</v>
+        <v>-0.5059</v>
       </c>
       <c r="J141" t="n">
-        <v>-15.8079</v>
+        <v>-14.6711</v>
       </c>
     </row>
     <row r="142">
@@ -7569,10 +7569,10 @@
         <v>1.08</v>
       </c>
       <c r="I142" t="n">
-        <v>0.2784</v>
+        <v>0.2383</v>
       </c>
       <c r="J142" t="n">
-        <v>6.1248</v>
+        <v>5.2426</v>
       </c>
     </row>
     <row r="143">
@@ -7609,10 +7609,10 @@
         <v>0.91</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.1123</v>
+        <v>-0.0977</v>
       </c>
       <c r="J143" t="n">
-        <v>-2.4706</v>
+        <v>-2.1494</v>
       </c>
     </row>
     <row r="144">
@@ -7649,10 +7649,10 @@
         <v>0.71</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.3149</v>
+        <v>-0.2989</v>
       </c>
       <c r="J144" t="n">
-        <v>-6.9278</v>
+        <v>-6.5758</v>
       </c>
     </row>
     <row r="145">
@@ -7689,10 +7689,10 @@
         <v>0.66</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.3604</v>
+        <v>-0.3463</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.9288</v>
+        <v>-7.6186</v>
       </c>
     </row>
     <row r="146">
@@ -7729,10 +7729,10 @@
         <v>0.48</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5195</v>
+        <v>-0.5208</v>
       </c>
       <c r="J146" t="n">
-        <v>-11.429</v>
+        <v>-11.4576</v>
       </c>
     </row>
     <row r="147">
@@ -7769,10 +7769,10 @@
         <v>1.61</v>
       </c>
       <c r="I147" t="n">
-        <v>1.2166</v>
+        <v>1.233</v>
       </c>
       <c r="J147" t="n">
-        <v>26.7652</v>
+        <v>27.126</v>
       </c>
     </row>
     <row r="148">
@@ -7809,10 +7809,10 @@
         <v>1.58</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1781</v>
+        <v>1.1935</v>
       </c>
       <c r="J148" t="n">
-        <v>25.9182</v>
+        <v>26.257</v>
       </c>
     </row>
     <row r="149">
@@ -7849,10 +7849,10 @@
         <v>1.35</v>
       </c>
       <c r="I149" t="n">
-        <v>0.8268</v>
+        <v>0.8127</v>
       </c>
       <c r="J149" t="n">
-        <v>18.1896</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="150">
@@ -7889,10 +7889,10 @@
         <v>1.2</v>
       </c>
       <c r="I150" t="n">
-        <v>0.5206</v>
+        <v>0.4918</v>
       </c>
       <c r="J150" t="n">
-        <v>11.4532</v>
+        <v>10.8196</v>
       </c>
     </row>
     <row r="151">
@@ -7929,10 +7929,10 @@
         <v>1.16</v>
       </c>
       <c r="I151" t="n">
-        <v>0.4295</v>
+        <v>0.3984</v>
       </c>
       <c r="J151" t="n">
-        <v>9.449</v>
+        <v>8.764799999999999</v>
       </c>
     </row>
     <row r="152">
@@ -7969,10 +7969,10 @@
         <v>1.98</v>
       </c>
       <c r="I152" t="n">
-        <v>1.7639</v>
+        <v>1.8392</v>
       </c>
       <c r="J152" t="n">
-        <v>51.1531</v>
+        <v>53.3368</v>
       </c>
     </row>
     <row r="153">
@@ -8009,10 +8009,10 @@
         <v>1.05</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1854</v>
+        <v>0.1568</v>
       </c>
       <c r="J153" t="n">
-        <v>5.3766</v>
+        <v>4.5472</v>
       </c>
     </row>
     <row r="154">
@@ -8049,10 +8049,10 @@
         <v>0.97</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.1544</v>
+        <v>-0.1232</v>
       </c>
       <c r="J154" t="n">
-        <v>-4.4776</v>
+        <v>-3.5728</v>
       </c>
     </row>
     <row r="155">
@@ -8089,10 +8089,10 @@
         <v>0.92</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3083</v>
+        <v>-0.2669</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.9407</v>
+        <v>-7.7401</v>
       </c>
     </row>
     <row r="156">
@@ -8129,10 +8129,10 @@
         <v>0.61</v>
       </c>
       <c r="I156" t="n">
-        <v>-1.0158</v>
+        <v>-1.017</v>
       </c>
       <c r="J156" t="n">
-        <v>-29.4582</v>
+        <v>-29.493</v>
       </c>
     </row>
     <row r="157">
@@ -8169,10 +8169,10 @@
         <v>1.12</v>
       </c>
       <c r="I157" t="n">
-        <v>0.2971</v>
+        <v>0.2465</v>
       </c>
       <c r="J157" t="n">
-        <v>8.6159</v>
+        <v>7.1485</v>
       </c>
     </row>
     <row r="158">
@@ -8209,10 +8209,10 @@
         <v>1.07</v>
       </c>
       <c r="I158" t="n">
-        <v>0.1968</v>
+        <v>0.1558</v>
       </c>
       <c r="J158" t="n">
-        <v>5.7072</v>
+        <v>4.5182</v>
       </c>
     </row>
     <row r="159">
@@ -8249,10 +8249,10 @@
         <v>0.97</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.0565</v>
+        <v>-0.0448</v>
       </c>
       <c r="J159" t="n">
-        <v>-1.6385</v>
+        <v>-1.2992</v>
       </c>
     </row>
     <row r="160">
@@ -8289,10 +8289,10 @@
         <v>0.86</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1882</v>
+        <v>-0.1678</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.4578</v>
+        <v>-4.8662</v>
       </c>
     </row>
     <row r="161">
@@ -8329,10 +8329,10 @@
         <v>0.83</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2195</v>
+        <v>-0.199</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.3655</v>
+        <v>-5.771</v>
       </c>
     </row>
     <row r="162">
@@ -8369,10 +8369,10 @@
         <v>1.61</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2265</v>
+        <v>1.2426</v>
       </c>
       <c r="J162" t="n">
-        <v>30.6625</v>
+        <v>31.065</v>
       </c>
     </row>
     <row r="163">
@@ -8409,10 +8409,10 @@
         <v>1.5</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0819</v>
+        <v>1.093</v>
       </c>
       <c r="J163" t="n">
-        <v>27.0475</v>
+        <v>27.325</v>
       </c>
     </row>
     <row r="164">
@@ -8449,10 +8449,10 @@
         <v>1.24</v>
       </c>
       <c r="I164" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.5886</v>
       </c>
       <c r="J164" t="n">
-        <v>15.385</v>
+        <v>14.715</v>
       </c>
     </row>
     <row r="165">
@@ -8489,10 +8489,10 @@
         <v>1.2</v>
       </c>
       <c r="I165" t="n">
-        <v>0.5293</v>
+        <v>0.4997</v>
       </c>
       <c r="J165" t="n">
-        <v>13.2325</v>
+        <v>12.4925</v>
       </c>
     </row>
     <row r="166">
@@ -8529,10 +8529,10 @@
         <v>1.06</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1794</v>
+        <v>0.1514</v>
       </c>
       <c r="J166" t="n">
-        <v>4.485</v>
+        <v>3.785</v>
       </c>
     </row>
     <row r="167">
@@ -8569,10 +8569,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0646</v>
+        <v>-0.0503</v>
       </c>
       <c r="J167" t="n">
-        <v>-1.615</v>
+        <v>-1.2575</v>
       </c>
     </row>
     <row r="168">
@@ -8609,10 +8609,10 @@
         <v>0.84</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1841</v>
+        <v>-0.1686</v>
       </c>
       <c r="J168" t="n">
-        <v>-4.6025</v>
+        <v>-4.215</v>
       </c>
     </row>
     <row r="169">
@@ -8649,10 +8649,10 @@
         <v>0.76</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2652</v>
+        <v>-0.2503</v>
       </c>
       <c r="J169" t="n">
-        <v>-6.63</v>
+        <v>-6.2575</v>
       </c>
     </row>
     <row r="170">
@@ -8689,10 +8689,10 @@
         <v>0.55</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4529</v>
+        <v>-0.4461</v>
       </c>
       <c r="J170" t="n">
-        <v>-11.3225</v>
+        <v>-11.1525</v>
       </c>
     </row>
     <row r="171">
@@ -8729,10 +8729,10 @@
         <v>0.52</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4793</v>
+        <v>-0.4752</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.9825</v>
+        <v>-11.88</v>
       </c>
     </row>
     <row r="172">
@@ -8769,10 +8769,10 @@
         <v>0.52</v>
       </c>
       <c r="I172" t="n">
-        <v>-0.4475</v>
+        <v>-0.4465</v>
       </c>
       <c r="J172" t="n">
-        <v>-8.5025</v>
+        <v>-8.483499999999999</v>
       </c>
     </row>
     <row r="173">
@@ -8809,10 +8809,10 @@
         <v>0.52</v>
       </c>
       <c r="I173" t="n">
-        <v>-0.4475</v>
+        <v>-0.4465</v>
       </c>
       <c r="J173" t="n">
-        <v>-8.5025</v>
+        <v>-8.483499999999999</v>
       </c>
     </row>
     <row r="174">
@@ -8849,10 +8849,10 @@
         <v>0.5</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.4646</v>
+        <v>-0.4641</v>
       </c>
       <c r="J174" t="n">
-        <v>-8.827400000000001</v>
+        <v>-8.8179</v>
       </c>
     </row>
     <row r="175">
@@ -8889,10 +8889,10 @@
         <v>0.47</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4889</v>
+        <v>-0.4891</v>
       </c>
       <c r="J175" t="n">
-        <v>-9.289099999999999</v>
+        <v>-9.292899999999999</v>
       </c>
     </row>
     <row r="176">
@@ -8929,10 +8929,10 @@
         <v>0.44</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5147</v>
+        <v>-0.5161</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.779299999999999</v>
+        <v>-9.805899999999999</v>
       </c>
     </row>
     <row r="177">
@@ -8969,10 +8969,10 @@
         <v>1.59</v>
       </c>
       <c r="I177" t="n">
-        <v>1.173</v>
+        <v>1.1924</v>
       </c>
       <c r="J177" t="n">
-        <v>22.287</v>
+        <v>22.6556</v>
       </c>
     </row>
     <row r="178">
@@ -9009,10 +9009,10 @@
         <v>1.58</v>
       </c>
       <c r="I178" t="n">
-        <v>1.1606</v>
+        <v>1.1799</v>
       </c>
       <c r="J178" t="n">
-        <v>22.0514</v>
+        <v>22.4181</v>
       </c>
     </row>
     <row r="179">
@@ -9049,10 +9049,10 @@
         <v>1.57</v>
       </c>
       <c r="I179" t="n">
-        <v>1.1482</v>
+        <v>1.1674</v>
       </c>
       <c r="J179" t="n">
-        <v>21.8158</v>
+        <v>22.1806</v>
       </c>
     </row>
     <row r="180">
@@ -9089,10 +9089,10 @@
         <v>1.46</v>
       </c>
       <c r="I180" t="n">
-        <v>1.0042</v>
+        <v>1.0139</v>
       </c>
       <c r="J180" t="n">
-        <v>19.0798</v>
+        <v>19.2641</v>
       </c>
     </row>
     <row r="181">
@@ -9129,10 +9129,10 @@
         <v>1.44</v>
       </c>
       <c r="I181" t="n">
-        <v>0.9725</v>
+        <v>0.9779</v>
       </c>
       <c r="J181" t="n">
-        <v>18.4775</v>
+        <v>18.5801</v>
       </c>
     </row>
   </sheetData>
